--- a/PLATEWARE PULL SHEET - TEMPLATE.xlsx
+++ b/PLATEWARE PULL SHEET - TEMPLATE.xlsx
@@ -8,13 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/davidcuvin/purveyor_project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04F4AE5E-F8B7-E646-8B2C-491D6031B7BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91C7CEA0-039B-E74A-BECF-7723CFB13585}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1000" windowWidth="29940" windowHeight="17600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="980" windowWidth="29940" windowHeight="17600" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Pull_Sheet" sheetId="1" r:id="rId1"/>
+    <sheet name="Updated_Pull_Sheet" sheetId="3" r:id="rId1"/>
+    <sheet name="Pull_Sheet" sheetId="1" r:id="rId2"/>
+    <sheet name="Inventory" sheetId="2" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">Inventory!$A$1:$E$75</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
@@ -25,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="104">
   <si>
     <t>Event Name:             Event Date:</t>
   </si>
@@ -64,13 +69,286 @@
   </si>
   <si>
     <t>SERVICEWARES:</t>
+  </si>
+  <si>
+    <t>Astor B&amp;B</t>
+  </si>
+  <si>
+    <t>Ginori App</t>
+  </si>
+  <si>
+    <t>German App</t>
+  </si>
+  <si>
+    <t>Amado Plate</t>
+  </si>
+  <si>
+    <t>B&amp;B knife</t>
+  </si>
+  <si>
+    <t>Entree Fork</t>
+  </si>
+  <si>
+    <t>App Knife</t>
+  </si>
+  <si>
+    <t>Entree Knife</t>
+  </si>
+  <si>
+    <t>Steak Knife</t>
+  </si>
+  <si>
+    <t>Tea Spoon</t>
+  </si>
+  <si>
+    <t>Table Spoon</t>
+  </si>
+  <si>
+    <t>Charger Plates</t>
+  </si>
+  <si>
+    <t>Small Ginori Bowls</t>
+  </si>
+  <si>
+    <t>Large Giinori Bowls</t>
+  </si>
+  <si>
+    <t>Serving Forks</t>
+  </si>
+  <si>
+    <t>Serving Spoons</t>
+  </si>
+  <si>
+    <t>Salad Tongs</t>
+  </si>
+  <si>
+    <t>Bread Tongs</t>
+  </si>
+  <si>
+    <t>Ice Tongs</t>
+  </si>
+  <si>
+    <t>Spritz</t>
+  </si>
+  <si>
+    <t>Highball</t>
+  </si>
+  <si>
+    <t>Rocks</t>
+  </si>
+  <si>
+    <t>Wine</t>
+  </si>
+  <si>
+    <t>Coupe</t>
+  </si>
+  <si>
+    <t>Round Mauviels</t>
+  </si>
+  <si>
+    <t>Rectangular Mauviels</t>
+  </si>
+  <si>
+    <t>Bread Baskets</t>
+  </si>
+  <si>
+    <t>Shallow Mezze Dishes</t>
+  </si>
+  <si>
+    <t>Ceramic Ramekins</t>
+  </si>
+  <si>
+    <t>Glass Ramekins</t>
+  </si>
+  <si>
+    <t>4qt Chafer</t>
+  </si>
+  <si>
+    <t>Round Chafer Full Pan</t>
+  </si>
+  <si>
+    <t>Round Chafer Split Pan</t>
+  </si>
+  <si>
+    <t>White 3 Tier</t>
+  </si>
+  <si>
+    <t>Silver 2 Tier</t>
+  </si>
+  <si>
+    <t>French Onion Bowl</t>
+  </si>
+  <si>
+    <t>Pink Plates</t>
+  </si>
+  <si>
+    <t>Large Round Silver Pedestals</t>
+  </si>
+  <si>
+    <t>Dessert Pedestal</t>
+  </si>
+  <si>
+    <t>Tea Sandwich Round</t>
+  </si>
+  <si>
+    <t>Oval/Square Large Silver Trays</t>
+  </si>
+  <si>
+    <t>Silver 2 Tier Rect</t>
+  </si>
+  <si>
+    <t>Woks</t>
+  </si>
+  <si>
+    <t>Bamboo Baskets</t>
+  </si>
+  <si>
+    <t>Large Shells</t>
+  </si>
+  <si>
+    <t>Round Black Canape Tray</t>
+  </si>
+  <si>
+    <t>Metal Coupes</t>
+  </si>
+  <si>
+    <t>Oil Curetes</t>
+  </si>
+  <si>
+    <t>Grill</t>
+  </si>
+  <si>
+    <t>Small Ceramic Pitcher</t>
+  </si>
+  <si>
+    <t>Small IRD Tray</t>
+  </si>
+  <si>
+    <t>Single Water Tower</t>
+  </si>
+  <si>
+    <t>Double Water Tower</t>
+  </si>
+  <si>
+    <t>Tall Silver Tier</t>
+  </si>
+  <si>
+    <t>Short Silver Tier</t>
+  </si>
+  <si>
+    <t>Ginori Entrée</t>
+  </si>
+  <si>
+    <t xml:space="preserve">German Entree </t>
+  </si>
+  <si>
+    <t xml:space="preserve">App Fork </t>
+  </si>
+  <si>
+    <t>Roll-ups</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rental forks </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oval Mauviels </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boos Boards </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oval 15" platter </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sm Amado Bowls </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ginori Salad Bowls </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rental Ramekins </t>
+  </si>
+  <si>
+    <t>Lrg IRD Tray</t>
+  </si>
+  <si>
+    <t>Inventory Date: 2/15/26</t>
+  </si>
+  <si>
+    <t>German Dessert 8in</t>
+  </si>
+  <si>
+    <t>Ginori Rim Bowl</t>
+  </si>
+  <si>
+    <t>Ginori Charger Plates</t>
+  </si>
+  <si>
+    <t>Ginori Oval Platter</t>
+  </si>
+  <si>
+    <t>German Oval Platter</t>
+  </si>
+  <si>
+    <t>Med IRD Tray</t>
+  </si>
+  <si>
+    <t>Metal Coupes, 8in</t>
+  </si>
+  <si>
+    <t>Silver Passing Trays, Large</t>
+  </si>
+  <si>
+    <t>Silver Passing Trays, Small</t>
+  </si>
+  <si>
+    <t>Oval Mauviels, Silver</t>
+  </si>
+  <si>
+    <t>Oval Mauviels, Copper</t>
+  </si>
+  <si>
+    <t>Oval Mauviels, Small, Copper</t>
+  </si>
+  <si>
+    <t>Shellfish Tower Platter, Small</t>
+  </si>
+  <si>
+    <t>Shellfish Tower Platter, Medium</t>
+  </si>
+  <si>
+    <t>Shellfish Tower Platter, Large</t>
+  </si>
+  <si>
+    <t>Silver Octagon Tray, Small</t>
+  </si>
+  <si>
+    <t>Silver Octagon Tray, Medium</t>
+  </si>
+  <si>
+    <t>Silver Octagon Tray, Large</t>
+  </si>
+  <si>
+    <t>Silver 2 Tier, Round</t>
+  </si>
+  <si>
+    <t>Silver 2 Tier, Rectangle</t>
+  </si>
+  <si>
+    <t>Silver Leaf Tiers</t>
+  </si>
+  <si>
+    <t>Gold Round Passing Trays</t>
+  </si>
+  <si>
+    <t>Shot Glass</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -108,7 +386,6 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -120,6 +397,60 @@
     </font>
     <font>
       <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -545,7 +876,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="139">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -570,248 +901,398 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -831,6 +1312,133 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>838200</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1460500</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>660400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7DD4E620-90CC-884F-9589-33F501A03614}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="838200" y="63500"/>
+          <a:ext cx="622300" cy="596900"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>838200</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1460500</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>660400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{66C148C2-F6AB-2C47-A272-E40DA007DA99}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="838200" y="63500"/>
+          <a:ext cx="622300" cy="596900"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -875,6 +1483,72 @@
         <a:xfrm>
           <a:off x="838200" y="63500"/>
           <a:ext cx="622300" cy="596900"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>838200</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1790700</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>1124080</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E21D7F2D-A567-E549-9A9E-5AA58C7E5752}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="838200" y="63500"/>
+          <a:ext cx="952500" cy="1060580"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1093,7 +1767,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7283AA4-07FC-BE4E-A014-7B45B56A06CA}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -1101,12 +1775,12 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="30.5" style="2" customWidth="1"/>
-    <col min="2" max="2" width="21" style="2" customWidth="1"/>
-    <col min="3" max="3" width="20" style="2" customWidth="1"/>
+    <col min="2" max="2" width="21" style="103" customWidth="1"/>
+    <col min="3" max="3" width="20" style="103" customWidth="1"/>
     <col min="4" max="4" width="6.5" style="2" customWidth="1"/>
-    <col min="5" max="5" width="21" style="2" customWidth="1"/>
-    <col min="6" max="6" width="28.6640625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="19.83203125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="40.33203125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="28.6640625" style="103" customWidth="1"/>
+    <col min="7" max="7" width="19.83203125" style="103" customWidth="1"/>
     <col min="8" max="8" width="19.5" style="2" customWidth="1"/>
     <col min="9" max="9" width="26.1640625" style="2" customWidth="1"/>
     <col min="10" max="18" width="8.83203125" style="2" customWidth="1"/>
@@ -1114,15 +1788,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="60.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="86"/>
-      <c r="B1" s="87" t="s">
+      <c r="A1" s="31"/>
+      <c r="B1" s="118" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="88"/>
-      <c r="D1" s="84"/>
-      <c r="E1" s="84"/>
-      <c r="F1" s="84"/>
-      <c r="G1" s="85"/>
+      <c r="C1" s="119"/>
+      <c r="D1" s="120"/>
+      <c r="E1" s="120"/>
+      <c r="F1" s="120"/>
+      <c r="G1" s="121"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
@@ -1133,17 +1807,17 @@
       <c r="O1" s="1"/>
     </row>
     <row r="2" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="76" t="s">
+      <c r="A2" s="122" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="76"/>
-      <c r="C2" s="76"/>
-      <c r="D2" s="70"/>
-      <c r="E2" s="38" t="s">
+      <c r="B2" s="122"/>
+      <c r="C2" s="122"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="34"/>
-      <c r="G2" s="39"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="104"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
@@ -1154,7 +1828,7 @@
       <c r="O2" s="3"/>
     </row>
     <row r="3" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="40" t="s">
+      <c r="A3" s="16" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="4" t="s">
@@ -1163,14 +1837,14 @@
       <c r="C3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="71"/>
+      <c r="D3" s="27"/>
       <c r="E3" s="4" t="s">
         <v>4</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="G3" s="41" t="s">
+      <c r="G3" s="17" t="s">
         <v>2</v>
       </c>
       <c r="H3" s="3"/>
@@ -1183,13 +1857,13 @@
       <c r="O3" s="3"/>
     </row>
     <row r="4" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="42"/>
-      <c r="B4" s="27"/>
-      <c r="C4" s="27"/>
+      <c r="A4" s="35"/>
+      <c r="B4" s="91"/>
+      <c r="C4" s="91"/>
       <c r="D4" s="68"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="43"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="92"/>
+      <c r="G4" s="105"/>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
@@ -1200,13 +1874,13 @@
       <c r="O4" s="3"/>
     </row>
     <row r="5" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="42"/>
-      <c r="B5" s="10"/>
-      <c r="C5" s="23"/>
-      <c r="D5" s="72"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="43"/>
+      <c r="A5" s="35"/>
+      <c r="B5" s="92"/>
+      <c r="C5" s="93"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="35"/>
+      <c r="F5" s="92"/>
+      <c r="G5" s="105"/>
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
@@ -1217,13 +1891,13 @@
       <c r="O5" s="3"/>
     </row>
     <row r="6" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="42"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="23"/>
-      <c r="D6" s="72"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="43"/>
+      <c r="A6" s="35"/>
+      <c r="B6" s="92"/>
+      <c r="C6" s="93"/>
+      <c r="D6" s="69"/>
+      <c r="E6" s="35"/>
+      <c r="F6" s="92"/>
+      <c r="G6" s="105"/>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
@@ -1234,13 +1908,13 @@
       <c r="O6" s="3"/>
     </row>
     <row r="7" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="42"/>
-      <c r="B7" s="10"/>
-      <c r="C7" s="23"/>
-      <c r="D7" s="73"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="43"/>
+      <c r="A7" s="35"/>
+      <c r="B7" s="92"/>
+      <c r="C7" s="93"/>
+      <c r="D7" s="69"/>
+      <c r="E7" s="35"/>
+      <c r="F7" s="92"/>
+      <c r="G7" s="105"/>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
@@ -1251,13 +1925,13 @@
       <c r="O7" s="3"/>
     </row>
     <row r="8" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="42"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="23"/>
-      <c r="D8" s="73"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="44"/>
+      <c r="A8" s="35"/>
+      <c r="B8" s="92"/>
+      <c r="C8" s="93"/>
+      <c r="D8" s="69"/>
+      <c r="E8" s="35"/>
+      <c r="F8" s="92"/>
+      <c r="G8" s="105"/>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
@@ -1268,13 +1942,13 @@
       <c r="O8" s="3"/>
     </row>
     <row r="9" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="45"/>
-      <c r="B9" s="11"/>
-      <c r="C9" s="28"/>
-      <c r="D9" s="74"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="44"/>
+      <c r="A9" s="35"/>
+      <c r="B9" s="94"/>
+      <c r="C9" s="95"/>
+      <c r="D9" s="70"/>
+      <c r="E9" s="35"/>
+      <c r="F9" s="92"/>
+      <c r="G9" s="105"/>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
@@ -1285,13 +1959,13 @@
       <c r="O9" s="3"/>
     </row>
     <row r="10" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="42"/>
-      <c r="B10" s="10"/>
-      <c r="C10" s="23"/>
-      <c r="D10" s="73"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="44"/>
+      <c r="A10" s="35"/>
+      <c r="B10" s="92"/>
+      <c r="C10" s="93"/>
+      <c r="D10" s="69"/>
+      <c r="E10" s="35"/>
+      <c r="F10" s="92"/>
+      <c r="G10" s="105"/>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
@@ -1302,13 +1976,13 @@
       <c r="O10" s="3"/>
     </row>
     <row r="11" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="42"/>
-      <c r="B11" s="10"/>
-      <c r="C11" s="23"/>
-      <c r="D11" s="73"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="44"/>
+      <c r="A11" s="35"/>
+      <c r="B11" s="92"/>
+      <c r="C11" s="93"/>
+      <c r="D11" s="69"/>
+      <c r="E11" s="35"/>
+      <c r="F11" s="92"/>
+      <c r="G11" s="105"/>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
@@ -1319,13 +1993,13 @@
       <c r="O11" s="3"/>
     </row>
     <row r="12" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="42"/>
-      <c r="B12" s="10"/>
-      <c r="C12" s="23"/>
-      <c r="D12" s="73"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="44"/>
+      <c r="A12" s="35"/>
+      <c r="B12" s="92"/>
+      <c r="C12" s="93"/>
+      <c r="D12" s="69"/>
+      <c r="E12" s="35"/>
+      <c r="F12" s="92"/>
+      <c r="G12" s="105"/>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
@@ -1336,13 +2010,13 @@
       <c r="O12" s="3"/>
     </row>
     <row r="13" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="42"/>
-      <c r="B13" s="10"/>
-      <c r="C13" s="23"/>
-      <c r="D13" s="73"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="44"/>
+      <c r="A13" s="34"/>
+      <c r="B13" s="92"/>
+      <c r="C13" s="93"/>
+      <c r="D13" s="69"/>
+      <c r="E13" s="35"/>
+      <c r="F13" s="92"/>
+      <c r="G13" s="105"/>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
@@ -1353,13 +2027,13 @@
       <c r="O13" s="3"/>
     </row>
     <row r="14" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="42"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="23"/>
-      <c r="D14" s="73"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="44"/>
+      <c r="A14" s="33"/>
+      <c r="B14" s="96"/>
+      <c r="C14" s="93"/>
+      <c r="D14" s="71"/>
+      <c r="E14" s="72"/>
+      <c r="F14" s="92"/>
+      <c r="G14" s="105"/>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
@@ -1370,17 +2044,17 @@
       <c r="O14" s="3"/>
     </row>
     <row r="15" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="46" t="s">
+      <c r="A15" s="123" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="31"/>
-      <c r="C15" s="32"/>
-      <c r="D15" s="75"/>
-      <c r="E15" s="29" t="s">
+      <c r="B15" s="124"/>
+      <c r="C15" s="125"/>
+      <c r="D15" s="30"/>
+      <c r="E15" s="115" t="s">
         <v>7</v>
       </c>
-      <c r="F15" s="30"/>
-      <c r="G15" s="47"/>
+      <c r="F15" s="116"/>
+      <c r="G15" s="117"/>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
       <c r="J15" s="3"/>
@@ -1391,23 +2065,23 @@
       <c r="O15" s="3"/>
     </row>
     <row r="16" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="48" t="s">
+      <c r="A16" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="B16" s="19" t="s">
+      <c r="B16" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C16" s="20" t="s">
+      <c r="C16" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D16" s="75"/>
-      <c r="E16" s="16" t="s">
+      <c r="D16" s="30"/>
+      <c r="E16" s="9" t="s">
         <v>4</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="G16" s="49" t="s">
+      <c r="G16" s="20" t="s">
         <v>2</v>
       </c>
       <c r="H16" s="3"/>
@@ -1420,13 +2094,13 @@
       <c r="O16" s="3"/>
     </row>
     <row r="17" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="50"/>
-      <c r="B17" s="12"/>
-      <c r="C17" s="22"/>
-      <c r="D17" s="64"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="51"/>
+      <c r="A17" s="35"/>
+      <c r="B17" s="97"/>
+      <c r="C17" s="98"/>
+      <c r="D17" s="73"/>
+      <c r="E17" s="35"/>
+      <c r="F17" s="106"/>
+      <c r="G17" s="107"/>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
@@ -1437,13 +2111,13 @@
       <c r="O17" s="3"/>
     </row>
     <row r="18" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="50"/>
-      <c r="B18" s="12"/>
-      <c r="C18" s="22"/>
-      <c r="D18" s="64"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="51"/>
+      <c r="A18" s="35"/>
+      <c r="B18" s="97"/>
+      <c r="C18" s="98"/>
+      <c r="D18" s="73"/>
+      <c r="E18" s="35"/>
+      <c r="F18" s="106"/>
+      <c r="G18" s="107"/>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
       <c r="J18" s="3"/>
@@ -1454,13 +2128,13 @@
       <c r="O18" s="3"/>
     </row>
     <row r="19" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="50"/>
-      <c r="B19" s="12"/>
-      <c r="C19" s="22"/>
-      <c r="D19" s="64"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="51"/>
+      <c r="A19" s="35"/>
+      <c r="B19" s="97"/>
+      <c r="C19" s="98"/>
+      <c r="D19" s="73"/>
+      <c r="E19" s="35"/>
+      <c r="F19" s="106"/>
+      <c r="G19" s="107"/>
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
@@ -1471,13 +2145,13 @@
       <c r="O19" s="3"/>
     </row>
     <row r="20" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="50"/>
-      <c r="B20" s="12"/>
-      <c r="C20" s="22"/>
-      <c r="D20" s="64"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="51"/>
+      <c r="A20" s="35"/>
+      <c r="B20" s="97"/>
+      <c r="C20" s="98"/>
+      <c r="D20" s="73"/>
+      <c r="E20" s="35"/>
+      <c r="F20" s="106"/>
+      <c r="G20" s="107"/>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
       <c r="J20" s="3"/>
@@ -1488,13 +2162,13 @@
       <c r="O20" s="3"/>
     </row>
     <row r="21" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="42"/>
-      <c r="B21" s="10"/>
-      <c r="C21" s="23"/>
-      <c r="D21" s="73"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="6"/>
-      <c r="G21" s="44"/>
+      <c r="A21" s="35"/>
+      <c r="B21" s="96"/>
+      <c r="C21" s="93"/>
+      <c r="D21" s="71"/>
+      <c r="E21" s="35"/>
+      <c r="F21" s="92"/>
+      <c r="G21" s="105"/>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
@@ -1505,13 +2179,13 @@
       <c r="O21" s="3"/>
     </row>
     <row r="22" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="42"/>
-      <c r="B22" s="10"/>
-      <c r="C22" s="23"/>
-      <c r="D22" s="73"/>
-      <c r="E22" s="24"/>
-      <c r="F22" s="6"/>
-      <c r="G22" s="44"/>
+      <c r="A22" s="33"/>
+      <c r="B22" s="96"/>
+      <c r="C22" s="93"/>
+      <c r="D22" s="71"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="92"/>
+      <c r="G22" s="105"/>
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
       <c r="J22" s="3"/>
@@ -1522,13 +2196,13 @@
       <c r="O22" s="3"/>
     </row>
     <row r="23" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="52"/>
-      <c r="B23" s="26"/>
-      <c r="C23" s="35"/>
-      <c r="D23" s="73"/>
-      <c r="E23" s="24"/>
-      <c r="F23" s="36"/>
-      <c r="G23" s="53"/>
+      <c r="A23" s="75"/>
+      <c r="B23" s="99"/>
+      <c r="C23" s="100"/>
+      <c r="D23" s="71"/>
+      <c r="E23" s="76"/>
+      <c r="F23" s="108"/>
+      <c r="G23" s="109"/>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
@@ -1539,15 +2213,15 @@
       <c r="O23" s="3"/>
     </row>
     <row r="24" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="77" t="s">
+      <c r="A24" s="126" t="s">
         <v>12</v>
       </c>
-      <c r="B24" s="21"/>
-      <c r="C24" s="21"/>
-      <c r="D24" s="21"/>
-      <c r="E24" s="21"/>
-      <c r="F24" s="21"/>
-      <c r="G24" s="78"/>
+      <c r="B24" s="127"/>
+      <c r="C24" s="127"/>
+      <c r="D24" s="127"/>
+      <c r="E24" s="127"/>
+      <c r="F24" s="127"/>
+      <c r="G24" s="128"/>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
       <c r="J24" s="3"/>
@@ -1561,23 +2235,23 @@
       <c r="R24" s="3"/>
     </row>
     <row r="25" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="54" t="s">
+      <c r="A25" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="B25" s="37" t="s">
+      <c r="B25" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C25" s="37" t="s">
+      <c r="C25" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D25" s="67"/>
-      <c r="E25" s="37" t="s">
+      <c r="D25" s="25"/>
+      <c r="E25" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F25" s="37" t="s">
+      <c r="F25" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="G25" s="55" t="s">
+      <c r="G25" s="23" t="s">
         <v>2</v>
       </c>
       <c r="H25" s="3"/>
@@ -1593,13 +2267,13 @@
       <c r="R25" s="3"/>
     </row>
     <row r="26" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="56"/>
-      <c r="B26" s="27"/>
-      <c r="C26" s="27"/>
+      <c r="A26" s="35"/>
+      <c r="B26" s="91"/>
+      <c r="C26" s="91"/>
       <c r="D26" s="68"/>
-      <c r="E26" s="27"/>
-      <c r="F26" s="27"/>
-      <c r="G26" s="57"/>
+      <c r="E26" s="35"/>
+      <c r="F26" s="91"/>
+      <c r="G26" s="110"/>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
       <c r="J26" s="3"/>
@@ -1613,13 +2287,13 @@
       <c r="R26" s="3"/>
     </row>
     <row r="27" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="56"/>
-      <c r="B27" s="27"/>
-      <c r="C27" s="27"/>
+      <c r="A27" s="35"/>
+      <c r="B27" s="91"/>
+      <c r="C27" s="91"/>
       <c r="D27" s="68"/>
-      <c r="E27" s="27"/>
-      <c r="F27" s="27"/>
-      <c r="G27" s="57"/>
+      <c r="E27" s="35"/>
+      <c r="F27" s="91"/>
+      <c r="G27" s="110"/>
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
       <c r="J27" s="3"/>
@@ -1633,13 +2307,13 @@
       <c r="R27" s="3"/>
     </row>
     <row r="28" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="56"/>
-      <c r="B28" s="27"/>
-      <c r="C28" s="27"/>
+      <c r="A28" s="35"/>
+      <c r="B28" s="91"/>
+      <c r="C28" s="91"/>
       <c r="D28" s="68"/>
-      <c r="E28" s="27"/>
-      <c r="F28" s="27"/>
-      <c r="G28" s="57"/>
+      <c r="E28" s="35"/>
+      <c r="F28" s="91"/>
+      <c r="G28" s="110"/>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
       <c r="J28" s="3"/>
@@ -1653,13 +2327,13 @@
       <c r="R28" s="3"/>
     </row>
     <row r="29" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="56"/>
-      <c r="B29" s="27"/>
-      <c r="C29" s="27"/>
+      <c r="A29" s="35"/>
+      <c r="B29" s="91"/>
+      <c r="C29" s="91"/>
       <c r="D29" s="68"/>
-      <c r="E29" s="27"/>
-      <c r="F29" s="27"/>
-      <c r="G29" s="57"/>
+      <c r="E29" s="35"/>
+      <c r="F29" s="91"/>
+      <c r="G29" s="110"/>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
       <c r="J29" s="3"/>
@@ -1673,13 +2347,13 @@
       <c r="R29" s="3"/>
     </row>
     <row r="30" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="56"/>
-      <c r="B30" s="27"/>
-      <c r="C30" s="27"/>
+      <c r="A30" s="35"/>
+      <c r="B30" s="91"/>
+      <c r="C30" s="91"/>
       <c r="D30" s="68"/>
-      <c r="E30" s="27"/>
-      <c r="F30" s="27"/>
-      <c r="G30" s="57"/>
+      <c r="E30" s="35"/>
+      <c r="F30" s="91"/>
+      <c r="G30" s="110"/>
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
       <c r="J30" s="3"/>
@@ -1693,13 +2367,13 @@
       <c r="R30" s="3"/>
     </row>
     <row r="31" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="56"/>
-      <c r="B31" s="27"/>
-      <c r="C31" s="27"/>
+      <c r="A31" s="35"/>
+      <c r="B31" s="91"/>
+      <c r="C31" s="91"/>
       <c r="D31" s="68"/>
-      <c r="E31" s="27"/>
-      <c r="F31" s="27"/>
-      <c r="G31" s="57"/>
+      <c r="E31" s="35"/>
+      <c r="F31" s="91"/>
+      <c r="G31" s="110"/>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
       <c r="J31" s="3"/>
@@ -1713,13 +2387,13 @@
       <c r="R31" s="3"/>
     </row>
     <row r="32" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="56"/>
-      <c r="B32" s="27"/>
-      <c r="C32" s="27"/>
+      <c r="A32" s="35"/>
+      <c r="B32" s="91"/>
+      <c r="C32" s="91"/>
       <c r="D32" s="68"/>
-      <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
-      <c r="G32" s="57"/>
+      <c r="E32" s="35"/>
+      <c r="F32" s="91"/>
+      <c r="G32" s="110"/>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
       <c r="J32" s="3"/>
@@ -1733,13 +2407,13 @@
       <c r="R32" s="3"/>
     </row>
     <row r="33" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="56"/>
-      <c r="B33" s="27"/>
-      <c r="C33" s="27"/>
+      <c r="A33" s="35"/>
+      <c r="B33" s="91"/>
+      <c r="C33" s="91"/>
       <c r="D33" s="68"/>
-      <c r="E33" s="27"/>
-      <c r="F33" s="27"/>
-      <c r="G33" s="57"/>
+      <c r="E33" s="35"/>
+      <c r="F33" s="91"/>
+      <c r="G33" s="110"/>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
       <c r="J33" s="3"/>
@@ -1753,13 +2427,13 @@
       <c r="R33" s="3"/>
     </row>
     <row r="34" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="56"/>
-      <c r="B34" s="27"/>
-      <c r="C34" s="27"/>
+      <c r="A34" s="35"/>
+      <c r="B34" s="91"/>
+      <c r="C34" s="91"/>
       <c r="D34" s="68"/>
-      <c r="E34" s="27"/>
-      <c r="F34" s="27"/>
-      <c r="G34" s="57"/>
+      <c r="E34" s="35"/>
+      <c r="F34" s="91"/>
+      <c r="G34" s="110"/>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3"/>
@@ -1773,13 +2447,13 @@
       <c r="R34" s="3"/>
     </row>
     <row r="35" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="56"/>
-      <c r="B35" s="27"/>
-      <c r="C35" s="27"/>
+      <c r="A35" s="35"/>
+      <c r="B35" s="91"/>
+      <c r="C35" s="91"/>
       <c r="D35" s="68"/>
-      <c r="E35" s="27"/>
-      <c r="F35" s="27"/>
-      <c r="G35" s="57"/>
+      <c r="E35" s="35"/>
+      <c r="F35" s="91"/>
+      <c r="G35" s="110"/>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
       <c r="J35" s="3"/>
@@ -1793,13 +2467,13 @@
       <c r="R35" s="3"/>
     </row>
     <row r="36" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="56"/>
-      <c r="B36" s="27"/>
-      <c r="C36" s="27"/>
+      <c r="A36" s="35"/>
+      <c r="B36" s="91"/>
+      <c r="C36" s="91"/>
       <c r="D36" s="68"/>
-      <c r="E36" s="27"/>
-      <c r="F36" s="27"/>
-      <c r="G36" s="57"/>
+      <c r="E36" s="35"/>
+      <c r="F36" s="91"/>
+      <c r="G36" s="110"/>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
       <c r="J36" s="3"/>
@@ -1813,13 +2487,13 @@
       <c r="R36" s="3"/>
     </row>
     <row r="37" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="56"/>
-      <c r="B37" s="27"/>
-      <c r="C37" s="27"/>
+      <c r="A37" s="35"/>
+      <c r="B37" s="91"/>
+      <c r="C37" s="91"/>
       <c r="D37" s="68"/>
-      <c r="E37" s="27"/>
-      <c r="F37" s="27"/>
-      <c r="G37" s="57"/>
+      <c r="E37" s="35"/>
+      <c r="F37" s="91"/>
+      <c r="G37" s="110"/>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
       <c r="J37" s="3"/>
@@ -1833,13 +2507,13 @@
       <c r="R37" s="3"/>
     </row>
     <row r="38" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="56"/>
-      <c r="B38" s="27"/>
-      <c r="C38" s="27"/>
+      <c r="A38" s="35"/>
+      <c r="B38" s="91"/>
+      <c r="C38" s="91"/>
       <c r="D38" s="68"/>
-      <c r="E38" s="27"/>
-      <c r="F38" s="27"/>
-      <c r="G38" s="57"/>
+      <c r="E38" s="35"/>
+      <c r="F38" s="91"/>
+      <c r="G38" s="110"/>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
       <c r="J38" s="3"/>
@@ -1853,13 +2527,13 @@
       <c r="R38" s="3"/>
     </row>
     <row r="39" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="56"/>
-      <c r="B39" s="27"/>
-      <c r="C39" s="27"/>
+      <c r="A39" s="35"/>
+      <c r="B39" s="91"/>
+      <c r="C39" s="91"/>
       <c r="D39" s="68"/>
-      <c r="E39" s="27"/>
-      <c r="F39" s="27"/>
-      <c r="G39" s="57"/>
+      <c r="E39" s="35"/>
+      <c r="F39" s="91"/>
+      <c r="G39" s="110"/>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
@@ -1873,13 +2547,13 @@
       <c r="R39" s="3"/>
     </row>
     <row r="40" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="56"/>
-      <c r="B40" s="27"/>
-      <c r="C40" s="27"/>
+      <c r="A40" s="35"/>
+      <c r="B40" s="91"/>
+      <c r="C40" s="91"/>
       <c r="D40" s="68"/>
-      <c r="E40" s="27"/>
-      <c r="F40" s="27"/>
-      <c r="G40" s="57"/>
+      <c r="E40" s="35"/>
+      <c r="F40" s="91"/>
+      <c r="G40" s="110"/>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
@@ -1893,13 +2567,13 @@
       <c r="R40" s="3"/>
     </row>
     <row r="41" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="56"/>
-      <c r="B41" s="27"/>
-      <c r="C41" s="27"/>
+      <c r="A41" s="35"/>
+      <c r="B41" s="91"/>
+      <c r="C41" s="91"/>
       <c r="D41" s="68"/>
-      <c r="E41" s="27"/>
-      <c r="F41" s="27"/>
-      <c r="G41" s="57"/>
+      <c r="E41" s="35"/>
+      <c r="F41" s="91"/>
+      <c r="G41" s="110"/>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
       <c r="J41" s="3"/>
@@ -1913,13 +2587,13 @@
       <c r="R41" s="3"/>
     </row>
     <row r="42" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="56"/>
-      <c r="B42" s="27"/>
-      <c r="C42" s="27"/>
+      <c r="A42" s="77"/>
+      <c r="B42" s="91"/>
+      <c r="C42" s="91"/>
       <c r="D42" s="68"/>
-      <c r="E42" s="27"/>
-      <c r="F42" s="27"/>
-      <c r="G42" s="57"/>
+      <c r="E42" s="32"/>
+      <c r="F42" s="91"/>
+      <c r="G42" s="110"/>
       <c r="H42" s="3"/>
       <c r="I42" s="3"/>
       <c r="J42" s="3"/>
@@ -1933,13 +2607,13 @@
       <c r="R42" s="3"/>
     </row>
     <row r="43" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="56"/>
-      <c r="B43" s="27"/>
-      <c r="C43" s="27"/>
+      <c r="A43" s="77"/>
+      <c r="B43" s="91"/>
+      <c r="C43" s="91"/>
       <c r="D43" s="68"/>
-      <c r="E43" s="27"/>
-      <c r="F43" s="27"/>
-      <c r="G43" s="57"/>
+      <c r="E43" s="32"/>
+      <c r="F43" s="91"/>
+      <c r="G43" s="110"/>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
       <c r="J43" s="3"/>
@@ -1953,17 +2627,17 @@
       <c r="R43" s="3"/>
     </row>
     <row r="44" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="81" t="s">
+      <c r="A44" s="113" t="s">
         <v>8</v>
       </c>
-      <c r="B44" s="79"/>
-      <c r="C44" s="79"/>
-      <c r="D44" s="67"/>
-      <c r="E44" s="79" t="s">
+      <c r="B44" s="114"/>
+      <c r="C44" s="114"/>
+      <c r="D44" s="25"/>
+      <c r="E44" s="114" t="s">
         <v>9</v>
       </c>
-      <c r="F44" s="79"/>
-      <c r="G44" s="82"/>
+      <c r="F44" s="114"/>
+      <c r="G44" s="129"/>
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>
       <c r="J44" s="3"/>
@@ -1977,7 +2651,7 @@
       <c r="R44" s="3"/>
     </row>
     <row r="45" spans="1:18" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="48" t="s">
+      <c r="A45" s="19" t="s">
         <v>4</v>
       </c>
       <c r="B45" s="4" t="s">
@@ -1986,14 +2660,14 @@
       <c r="C45" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D45" s="67"/>
+      <c r="D45" s="25"/>
       <c r="E45" s="7" t="s">
         <v>4</v>
       </c>
       <c r="F45" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="G45" s="49" t="s">
+      <c r="G45" s="20" t="s">
         <v>2</v>
       </c>
       <c r="H45" s="3"/>
@@ -2009,13 +2683,13 @@
       <c r="R45" s="3"/>
     </row>
     <row r="46" spans="1:18" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="50"/>
-      <c r="B46" s="12"/>
-      <c r="C46" s="22"/>
-      <c r="D46" s="69"/>
-      <c r="E46" s="8"/>
-      <c r="F46" s="8"/>
-      <c r="G46" s="51"/>
+      <c r="A46" s="35"/>
+      <c r="B46" s="97"/>
+      <c r="C46" s="98"/>
+      <c r="D46" s="78"/>
+      <c r="E46" s="74"/>
+      <c r="F46" s="106"/>
+      <c r="G46" s="107"/>
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
       <c r="J46" s="3"/>
@@ -2029,13 +2703,13 @@
       <c r="R46" s="3"/>
     </row>
     <row r="47" spans="1:18" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="50"/>
-      <c r="B47" s="12"/>
-      <c r="C47" s="22"/>
-      <c r="D47" s="69"/>
-      <c r="E47" s="8"/>
-      <c r="F47" s="8"/>
-      <c r="G47" s="51"/>
+      <c r="A47" s="35"/>
+      <c r="B47" s="97"/>
+      <c r="C47" s="98"/>
+      <c r="D47" s="78"/>
+      <c r="E47" s="74"/>
+      <c r="F47" s="106"/>
+      <c r="G47" s="107"/>
       <c r="H47" s="3"/>
       <c r="I47" s="3"/>
       <c r="J47" s="3"/>
@@ -2049,13 +2723,13 @@
       <c r="R47" s="3"/>
     </row>
     <row r="48" spans="1:18" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="50"/>
-      <c r="B48" s="12"/>
-      <c r="C48" s="22"/>
-      <c r="D48" s="64"/>
-      <c r="E48" s="17"/>
-      <c r="F48" s="8"/>
-      <c r="G48" s="51"/>
+      <c r="A48" s="74"/>
+      <c r="B48" s="97"/>
+      <c r="C48" s="98"/>
+      <c r="D48" s="73"/>
+      <c r="E48" s="79"/>
+      <c r="F48" s="106"/>
+      <c r="G48" s="107"/>
       <c r="H48" s="3"/>
       <c r="I48" s="3"/>
       <c r="J48" s="3"/>
@@ -2069,13 +2743,13 @@
       <c r="R48" s="3"/>
     </row>
     <row r="49" spans="1:18" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="50"/>
-      <c r="B49" s="12"/>
-      <c r="C49" s="22"/>
-      <c r="D49" s="64"/>
-      <c r="E49" s="17"/>
-      <c r="F49" s="8"/>
-      <c r="G49" s="51"/>
+      <c r="A49" s="80"/>
+      <c r="B49" s="97"/>
+      <c r="C49" s="98"/>
+      <c r="D49" s="73"/>
+      <c r="E49" s="79"/>
+      <c r="F49" s="106"/>
+      <c r="G49" s="107"/>
       <c r="H49" s="3"/>
       <c r="I49" s="3"/>
       <c r="J49" s="3"/>
@@ -2089,13 +2763,13 @@
       <c r="R49" s="3"/>
     </row>
     <row r="50" spans="1:18" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="50"/>
-      <c r="B50" s="12"/>
-      <c r="C50" s="22"/>
-      <c r="D50" s="64"/>
-      <c r="E50" s="17"/>
-      <c r="F50" s="8"/>
-      <c r="G50" s="51"/>
+      <c r="A50" s="80"/>
+      <c r="B50" s="97"/>
+      <c r="C50" s="98"/>
+      <c r="D50" s="73"/>
+      <c r="E50" s="79"/>
+      <c r="F50" s="106"/>
+      <c r="G50" s="107"/>
       <c r="H50" s="3"/>
       <c r="I50" s="3"/>
       <c r="J50" s="3"/>
@@ -2109,13 +2783,13 @@
       <c r="R50" s="3"/>
     </row>
     <row r="51" spans="1:18" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="50"/>
-      <c r="B51" s="12"/>
-      <c r="C51" s="22"/>
-      <c r="D51" s="69"/>
-      <c r="E51" s="8"/>
-      <c r="F51" s="8"/>
-      <c r="G51" s="51"/>
+      <c r="A51" s="80"/>
+      <c r="B51" s="97"/>
+      <c r="C51" s="98"/>
+      <c r="D51" s="78"/>
+      <c r="E51" s="74"/>
+      <c r="F51" s="106"/>
+      <c r="G51" s="107"/>
       <c r="H51" s="3"/>
       <c r="I51" s="3"/>
       <c r="J51" s="3"/>
@@ -2129,182 +2803,182 @@
       <c r="R51" s="3"/>
     </row>
     <row r="52" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="81" t="s">
+      <c r="A52" s="113" t="s">
         <v>11</v>
       </c>
-      <c r="B52" s="79"/>
-      <c r="C52" s="79"/>
-      <c r="D52" s="64"/>
-      <c r="E52" s="29" t="s">
+      <c r="B52" s="114"/>
+      <c r="C52" s="114"/>
+      <c r="D52" s="24"/>
+      <c r="E52" s="115" t="s">
         <v>10</v>
       </c>
-      <c r="F52" s="30"/>
-      <c r="G52" s="47"/>
+      <c r="F52" s="116"/>
+      <c r="G52" s="117"/>
     </row>
     <row r="53" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="48" t="s">
+      <c r="A53" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="B53" s="19" t="s">
+      <c r="B53" s="10" t="s">
         <v>1</v>
       </c>
       <c r="C53" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D53" s="64"/>
-      <c r="E53" s="25" t="s">
+      <c r="D53" s="24"/>
+      <c r="E53" s="13" t="s">
         <v>4</v>
       </c>
       <c r="F53" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="G53" s="49" t="s">
+      <c r="G53" s="20" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="54" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="50"/>
-      <c r="B54" s="12"/>
-      <c r="C54" s="22"/>
-      <c r="D54" s="64"/>
-      <c r="E54" s="17"/>
-      <c r="F54" s="8"/>
-      <c r="G54" s="51"/>
+      <c r="A54" s="35"/>
+      <c r="B54" s="97"/>
+      <c r="C54" s="98"/>
+      <c r="D54" s="73"/>
+      <c r="E54" s="79"/>
+      <c r="F54" s="106"/>
+      <c r="G54" s="107"/>
     </row>
     <row r="55" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="50"/>
-      <c r="B55" s="12"/>
-      <c r="C55" s="22"/>
-      <c r="D55" s="64"/>
-      <c r="E55" s="17"/>
-      <c r="F55" s="8"/>
-      <c r="G55" s="51"/>
+      <c r="A55" s="35"/>
+      <c r="B55" s="97"/>
+      <c r="C55" s="98"/>
+      <c r="D55" s="73"/>
+      <c r="E55" s="79"/>
+      <c r="F55" s="106"/>
+      <c r="G55" s="107"/>
     </row>
     <row r="56" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="50"/>
-      <c r="B56" s="12"/>
-      <c r="C56" s="22"/>
-      <c r="D56" s="65"/>
-      <c r="E56" s="17"/>
-      <c r="F56" s="8"/>
-      <c r="G56" s="51"/>
+      <c r="A56" s="80"/>
+      <c r="B56" s="97"/>
+      <c r="C56" s="98"/>
+      <c r="D56" s="81"/>
+      <c r="E56" s="79"/>
+      <c r="F56" s="106"/>
+      <c r="G56" s="107"/>
     </row>
     <row r="57" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="58"/>
-      <c r="B57" s="13"/>
-      <c r="C57" s="33"/>
-      <c r="D57" s="65"/>
-      <c r="E57" s="18"/>
-      <c r="F57" s="9"/>
-      <c r="G57" s="59"/>
+      <c r="A57" s="82"/>
+      <c r="B57" s="101"/>
+      <c r="C57" s="102"/>
+      <c r="D57" s="81"/>
+      <c r="E57" s="83"/>
+      <c r="F57" s="91"/>
+      <c r="G57" s="110"/>
     </row>
     <row r="58" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="58"/>
-      <c r="B58" s="13"/>
-      <c r="C58" s="33"/>
-      <c r="D58" s="65"/>
-      <c r="E58" s="18"/>
-      <c r="F58" s="9"/>
-      <c r="G58" s="59"/>
+      <c r="A58" s="82"/>
+      <c r="B58" s="101"/>
+      <c r="C58" s="102"/>
+      <c r="D58" s="81"/>
+      <c r="E58" s="83"/>
+      <c r="F58" s="91"/>
+      <c r="G58" s="110"/>
     </row>
     <row r="59" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="58"/>
-      <c r="B59" s="13"/>
-      <c r="C59" s="33"/>
-      <c r="D59" s="65"/>
-      <c r="E59" s="18"/>
-      <c r="F59" s="9"/>
-      <c r="G59" s="59"/>
+      <c r="A59" s="82"/>
+      <c r="B59" s="101"/>
+      <c r="C59" s="102"/>
+      <c r="D59" s="81"/>
+      <c r="E59" s="83"/>
+      <c r="F59" s="91"/>
+      <c r="G59" s="110"/>
     </row>
     <row r="60" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="58"/>
-      <c r="B60" s="13"/>
-      <c r="C60" s="33"/>
-      <c r="D60" s="65"/>
-      <c r="E60" s="18"/>
-      <c r="F60" s="9"/>
-      <c r="G60" s="59"/>
+      <c r="A60" s="82"/>
+      <c r="B60" s="101"/>
+      <c r="C60" s="102"/>
+      <c r="D60" s="81"/>
+      <c r="E60" s="83"/>
+      <c r="F60" s="91"/>
+      <c r="G60" s="110"/>
     </row>
     <row r="61" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="58"/>
-      <c r="B61" s="13"/>
-      <c r="C61" s="33"/>
-      <c r="D61" s="65"/>
-      <c r="E61" s="18"/>
-      <c r="F61" s="9"/>
-      <c r="G61" s="59"/>
+      <c r="A61" s="82"/>
+      <c r="B61" s="101"/>
+      <c r="C61" s="102"/>
+      <c r="D61" s="81"/>
+      <c r="E61" s="83"/>
+      <c r="F61" s="91"/>
+      <c r="G61" s="110"/>
     </row>
     <row r="62" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="58"/>
-      <c r="B62" s="13"/>
-      <c r="C62" s="33"/>
-      <c r="D62" s="65"/>
-      <c r="E62" s="18"/>
-      <c r="F62" s="9"/>
-      <c r="G62" s="59"/>
+      <c r="A62" s="82"/>
+      <c r="B62" s="101"/>
+      <c r="C62" s="102"/>
+      <c r="D62" s="81"/>
+      <c r="E62" s="83"/>
+      <c r="F62" s="91"/>
+      <c r="G62" s="110"/>
     </row>
     <row r="63" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="58"/>
-      <c r="B63" s="13"/>
-      <c r="C63" s="33"/>
-      <c r="D63" s="65"/>
-      <c r="E63" s="18"/>
-      <c r="F63" s="9"/>
-      <c r="G63" s="59"/>
+      <c r="A63" s="82"/>
+      <c r="B63" s="101"/>
+      <c r="C63" s="102"/>
+      <c r="D63" s="81"/>
+      <c r="E63" s="83"/>
+      <c r="F63" s="91"/>
+      <c r="G63" s="110"/>
     </row>
     <row r="64" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="58"/>
-      <c r="B64" s="13"/>
-      <c r="C64" s="33"/>
-      <c r="D64" s="65"/>
-      <c r="E64" s="18"/>
-      <c r="F64" s="9"/>
-      <c r="G64" s="59"/>
+      <c r="A64" s="82"/>
+      <c r="B64" s="101"/>
+      <c r="C64" s="102"/>
+      <c r="D64" s="81"/>
+      <c r="E64" s="83"/>
+      <c r="F64" s="91"/>
+      <c r="G64" s="110"/>
     </row>
     <row r="65" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="58"/>
-      <c r="B65" s="13"/>
-      <c r="C65" s="33"/>
-      <c r="D65" s="66"/>
-      <c r="E65" s="9"/>
-      <c r="F65" s="9"/>
-      <c r="G65" s="59"/>
+      <c r="A65" s="82"/>
+      <c r="B65" s="101"/>
+      <c r="C65" s="102"/>
+      <c r="D65" s="85"/>
+      <c r="E65" s="84"/>
+      <c r="F65" s="91"/>
+      <c r="G65" s="110"/>
     </row>
     <row r="66" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="58"/>
-      <c r="B66" s="13"/>
-      <c r="C66" s="33"/>
-      <c r="D66" s="66"/>
-      <c r="E66" s="9"/>
-      <c r="F66" s="9"/>
-      <c r="G66" s="59"/>
+      <c r="A66" s="82"/>
+      <c r="B66" s="101"/>
+      <c r="C66" s="102"/>
+      <c r="D66" s="85"/>
+      <c r="E66" s="84"/>
+      <c r="F66" s="91"/>
+      <c r="G66" s="110"/>
     </row>
     <row r="67" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="58"/>
-      <c r="B67" s="13"/>
-      <c r="C67" s="33"/>
-      <c r="D67" s="66"/>
-      <c r="E67" s="9"/>
-      <c r="F67" s="9"/>
-      <c r="G67" s="59"/>
+      <c r="A67" s="82"/>
+      <c r="B67" s="101"/>
+      <c r="C67" s="102"/>
+      <c r="D67" s="85"/>
+      <c r="E67" s="84"/>
+      <c r="F67" s="91"/>
+      <c r="G67" s="110"/>
     </row>
     <row r="68" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="58"/>
-      <c r="B68" s="13"/>
-      <c r="C68" s="33"/>
-      <c r="D68" s="67"/>
-      <c r="E68" s="9"/>
-      <c r="F68" s="9"/>
-      <c r="G68" s="59"/>
+      <c r="A68" s="82"/>
+      <c r="B68" s="101"/>
+      <c r="C68" s="102"/>
+      <c r="D68" s="86"/>
+      <c r="E68" s="84"/>
+      <c r="F68" s="91"/>
+      <c r="G68" s="110"/>
     </row>
     <row r="69" spans="1:7" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="60"/>
-      <c r="B69" s="61"/>
-      <c r="C69" s="61"/>
-      <c r="D69" s="83"/>
-      <c r="E69" s="80"/>
-      <c r="F69" s="62"/>
-      <c r="G69" s="63"/>
+      <c r="A69" s="87"/>
+      <c r="B69" s="88"/>
+      <c r="C69" s="88"/>
+      <c r="D69" s="89"/>
+      <c r="E69" s="90"/>
+      <c r="F69" s="111"/>
+      <c r="G69" s="112"/>
     </row>
     <row r="70" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="71" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -3228,6 +3902,2293 @@
     <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="E52:G52"/>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="E15:G15"/>
+    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="E44:G44"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.25" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:R989"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="30.5" style="2" customWidth="1"/>
+    <col min="2" max="2" width="21" style="103" customWidth="1"/>
+    <col min="3" max="3" width="20" style="103" customWidth="1"/>
+    <col min="4" max="4" width="6.5" style="2" customWidth="1"/>
+    <col min="5" max="5" width="40.33203125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="28.6640625" style="103" customWidth="1"/>
+    <col min="7" max="7" width="19.83203125" style="103" customWidth="1"/>
+    <col min="8" max="8" width="19.5" style="2" customWidth="1"/>
+    <col min="9" max="9" width="26.1640625" style="2" customWidth="1"/>
+    <col min="10" max="18" width="8.83203125" style="2" customWidth="1"/>
+    <col min="19" max="16384" width="14.5" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" ht="60.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="31"/>
+      <c r="B1" s="118" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="119"/>
+      <c r="D1" s="120"/>
+      <c r="E1" s="120"/>
+      <c r="F1" s="120"/>
+      <c r="G1" s="121"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+    </row>
+    <row r="2" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="122" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="122"/>
+      <c r="C2" s="122"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="56"/>
+      <c r="G2" s="104"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+    </row>
+    <row r="3" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="27"/>
+      <c r="E3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
+    </row>
+    <row r="4" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="91"/>
+      <c r="C4" s="91"/>
+      <c r="D4" s="68"/>
+      <c r="E4" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="92"/>
+      <c r="G4" s="105"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3"/>
+      <c r="O4" s="3"/>
+    </row>
+    <row r="5" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="35" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="92"/>
+      <c r="C5" s="93"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="35" t="s">
+        <v>70</v>
+      </c>
+      <c r="F5" s="92"/>
+      <c r="G5" s="105"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="3"/>
+      <c r="N5" s="3"/>
+      <c r="O5" s="3"/>
+    </row>
+    <row r="6" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="B6" s="92"/>
+      <c r="C6" s="93"/>
+      <c r="D6" s="69"/>
+      <c r="E6" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="92"/>
+      <c r="G6" s="105"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="3"/>
+      <c r="N6" s="3"/>
+      <c r="O6" s="3"/>
+    </row>
+    <row r="7" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="92"/>
+      <c r="C7" s="93"/>
+      <c r="D7" s="69"/>
+      <c r="E7" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" s="92"/>
+      <c r="G7" s="105"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+    </row>
+    <row r="8" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="35" t="s">
+        <v>69</v>
+      </c>
+      <c r="B8" s="92"/>
+      <c r="C8" s="93"/>
+      <c r="D8" s="69"/>
+      <c r="E8" s="35" t="s">
+        <v>20</v>
+      </c>
+      <c r="F8" s="92"/>
+      <c r="G8" s="105"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="3"/>
+      <c r="O8" s="3"/>
+    </row>
+    <row r="9" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="94"/>
+      <c r="C9" s="95"/>
+      <c r="D9" s="70"/>
+      <c r="E9" s="35" t="s">
+        <v>21</v>
+      </c>
+      <c r="F9" s="92"/>
+      <c r="G9" s="105"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3"/>
+      <c r="N9" s="3"/>
+      <c r="O9" s="3"/>
+    </row>
+    <row r="10" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="35" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="92"/>
+      <c r="C10" s="93"/>
+      <c r="D10" s="69"/>
+      <c r="E10" s="35" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" s="92"/>
+      <c r="G10" s="105"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="3"/>
+      <c r="N10" s="3"/>
+      <c r="O10" s="3"/>
+    </row>
+    <row r="11" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="35" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="92"/>
+      <c r="C11" s="93"/>
+      <c r="D11" s="69"/>
+      <c r="E11" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="F11" s="92"/>
+      <c r="G11" s="105"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3"/>
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="92"/>
+      <c r="C12" s="93"/>
+      <c r="D12" s="69"/>
+      <c r="E12" s="35" t="s">
+        <v>71</v>
+      </c>
+      <c r="F12" s="92"/>
+      <c r="G12" s="105"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3"/>
+      <c r="L12" s="3"/>
+      <c r="M12" s="3"/>
+      <c r="N12" s="3"/>
+      <c r="O12" s="3"/>
+    </row>
+    <row r="13" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="34"/>
+      <c r="B13" s="92"/>
+      <c r="C13" s="93"/>
+      <c r="D13" s="69"/>
+      <c r="E13" s="35" t="s">
+        <v>72</v>
+      </c>
+      <c r="F13" s="92"/>
+      <c r="G13" s="105"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3"/>
+      <c r="K13" s="3"/>
+      <c r="L13" s="3"/>
+      <c r="M13" s="3"/>
+      <c r="N13" s="3"/>
+      <c r="O13" s="3"/>
+    </row>
+    <row r="14" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="33"/>
+      <c r="B14" s="96"/>
+      <c r="C14" s="93"/>
+      <c r="D14" s="71"/>
+      <c r="E14" s="72"/>
+      <c r="F14" s="92"/>
+      <c r="G14" s="105"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="3"/>
+      <c r="L14" s="3"/>
+      <c r="M14" s="3"/>
+      <c r="N14" s="3"/>
+      <c r="O14" s="3"/>
+    </row>
+    <row r="15" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="123" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" s="124"/>
+      <c r="C15" s="125"/>
+      <c r="D15" s="30"/>
+      <c r="E15" s="115" t="s">
+        <v>7</v>
+      </c>
+      <c r="F15" s="116"/>
+      <c r="G15" s="117"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="3"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="3"/>
+      <c r="N15" s="3"/>
+      <c r="O15" s="3"/>
+    </row>
+    <row r="16" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D16" s="30"/>
+      <c r="E16" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="G16" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="3"/>
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="35" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" s="97"/>
+      <c r="C17" s="98"/>
+      <c r="D17" s="73"/>
+      <c r="E17" s="35" t="s">
+        <v>32</v>
+      </c>
+      <c r="F17" s="106"/>
+      <c r="G17" s="107"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="3"/>
+      <c r="L17" s="3"/>
+      <c r="M17" s="3"/>
+      <c r="N17" s="3"/>
+      <c r="O17" s="3"/>
+    </row>
+    <row r="18" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="35" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" s="97"/>
+      <c r="C18" s="98"/>
+      <c r="D18" s="73"/>
+      <c r="E18" s="35" t="s">
+        <v>33</v>
+      </c>
+      <c r="F18" s="106"/>
+      <c r="G18" s="107"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3"/>
+      <c r="L18" s="3"/>
+      <c r="M18" s="3"/>
+      <c r="N18" s="3"/>
+      <c r="O18" s="3"/>
+    </row>
+    <row r="19" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="35" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" s="97"/>
+      <c r="C19" s="98"/>
+      <c r="D19" s="73"/>
+      <c r="E19" s="35" t="s">
+        <v>34</v>
+      </c>
+      <c r="F19" s="106"/>
+      <c r="G19" s="107"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="3"/>
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="35" t="s">
+        <v>30</v>
+      </c>
+      <c r="B20" s="97"/>
+      <c r="C20" s="98"/>
+      <c r="D20" s="73"/>
+      <c r="E20" s="35" t="s">
+        <v>35</v>
+      </c>
+      <c r="F20" s="106"/>
+      <c r="G20" s="107"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3"/>
+      <c r="J20" s="3"/>
+      <c r="K20" s="3"/>
+      <c r="L20" s="3"/>
+      <c r="M20" s="3"/>
+      <c r="N20" s="3"/>
+      <c r="O20" s="3"/>
+    </row>
+    <row r="21" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="35" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21" s="96"/>
+      <c r="C21" s="93"/>
+      <c r="D21" s="71"/>
+      <c r="E21" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="F21" s="92"/>
+      <c r="G21" s="105"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
+      <c r="J21" s="3"/>
+      <c r="K21" s="3"/>
+      <c r="L21" s="3"/>
+      <c r="M21" s="3"/>
+      <c r="N21" s="3"/>
+      <c r="O21" s="3"/>
+    </row>
+    <row r="22" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="33"/>
+      <c r="B22" s="96"/>
+      <c r="C22" s="93"/>
+      <c r="D22" s="71"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="92"/>
+      <c r="G22" s="105"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3"/>
+      <c r="L22" s="3"/>
+      <c r="M22" s="3"/>
+      <c r="N22" s="3"/>
+      <c r="O22" s="3"/>
+    </row>
+    <row r="23" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="75"/>
+      <c r="B23" s="99"/>
+      <c r="C23" s="100"/>
+      <c r="D23" s="71"/>
+      <c r="E23" s="76"/>
+      <c r="F23" s="108"/>
+      <c r="G23" s="109"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="3"/>
+      <c r="L23" s="3"/>
+      <c r="M23" s="3"/>
+      <c r="N23" s="3"/>
+      <c r="O23" s="3"/>
+    </row>
+    <row r="24" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="126" t="s">
+        <v>12</v>
+      </c>
+      <c r="B24" s="127"/>
+      <c r="C24" s="127"/>
+      <c r="D24" s="127"/>
+      <c r="E24" s="127"/>
+      <c r="F24" s="127"/>
+      <c r="G24" s="128"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3"/>
+      <c r="J24" s="3"/>
+      <c r="K24" s="3"/>
+      <c r="L24" s="3"/>
+      <c r="M24" s="3"/>
+      <c r="N24" s="3"/>
+      <c r="O24" s="3"/>
+      <c r="P24" s="3"/>
+      <c r="Q24" s="3"/>
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="C25" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="D25" s="25"/>
+      <c r="E25" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="F25" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="G25" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="H25" s="3"/>
+      <c r="I25" s="3"/>
+      <c r="J25" s="3"/>
+      <c r="K25" s="3"/>
+      <c r="L25" s="3"/>
+      <c r="M25" s="3"/>
+      <c r="N25" s="3"/>
+      <c r="O25" s="3"/>
+      <c r="P25" s="3"/>
+      <c r="Q25" s="3"/>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="35" t="s">
+        <v>73</v>
+      </c>
+      <c r="B26" s="91"/>
+      <c r="C26" s="91"/>
+      <c r="D26" s="68"/>
+      <c r="E26" s="35" t="s">
+        <v>48</v>
+      </c>
+      <c r="F26" s="91"/>
+      <c r="G26" s="110"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="3"/>
+      <c r="J26" s="3"/>
+      <c r="K26" s="3"/>
+      <c r="L26" s="3"/>
+      <c r="M26" s="3"/>
+      <c r="N26" s="3"/>
+      <c r="O26" s="3"/>
+      <c r="P26" s="3"/>
+      <c r="Q26" s="3"/>
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="35" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" s="91"/>
+      <c r="C27" s="91"/>
+      <c r="D27" s="68"/>
+      <c r="E27" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="F27" s="91"/>
+      <c r="G27" s="110"/>
+      <c r="H27" s="3"/>
+      <c r="I27" s="3"/>
+      <c r="J27" s="3"/>
+      <c r="K27" s="3"/>
+      <c r="L27" s="3"/>
+      <c r="M27" s="3"/>
+      <c r="N27" s="3"/>
+      <c r="O27" s="3"/>
+      <c r="P27" s="3"/>
+      <c r="Q27" s="3"/>
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" s="91"/>
+      <c r="C28" s="91"/>
+      <c r="D28" s="68"/>
+      <c r="E28" s="35" t="s">
+        <v>74</v>
+      </c>
+      <c r="F28" s="91"/>
+      <c r="G28" s="110"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="3"/>
+      <c r="J28" s="3"/>
+      <c r="K28" s="3"/>
+      <c r="L28" s="3"/>
+      <c r="M28" s="3"/>
+      <c r="N28" s="3"/>
+      <c r="O28" s="3"/>
+      <c r="P28" s="3"/>
+      <c r="Q28" s="3"/>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="35" t="s">
+        <v>75</v>
+      </c>
+      <c r="B29" s="91"/>
+      <c r="C29" s="91"/>
+      <c r="D29" s="68"/>
+      <c r="E29" s="35" t="s">
+        <v>50</v>
+      </c>
+      <c r="F29" s="91"/>
+      <c r="G29" s="110"/>
+      <c r="H29" s="3"/>
+      <c r="I29" s="3"/>
+      <c r="J29" s="3"/>
+      <c r="K29" s="3"/>
+      <c r="L29" s="3"/>
+      <c r="M29" s="3"/>
+      <c r="N29" s="3"/>
+      <c r="O29" s="3"/>
+      <c r="P29" s="3"/>
+      <c r="Q29" s="3"/>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="35" t="s">
+        <v>76</v>
+      </c>
+      <c r="B30" s="91"/>
+      <c r="C30" s="91"/>
+      <c r="D30" s="68"/>
+      <c r="E30" s="35" t="s">
+        <v>51</v>
+      </c>
+      <c r="F30" s="91"/>
+      <c r="G30" s="110"/>
+      <c r="H30" s="3"/>
+      <c r="I30" s="3"/>
+      <c r="J30" s="3"/>
+      <c r="K30" s="3"/>
+      <c r="L30" s="3"/>
+      <c r="M30" s="3"/>
+      <c r="N30" s="3"/>
+      <c r="O30" s="3"/>
+      <c r="P30" s="3"/>
+      <c r="Q30" s="3"/>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="B31" s="91"/>
+      <c r="C31" s="91"/>
+      <c r="D31" s="68"/>
+      <c r="E31" s="35" t="s">
+        <v>52</v>
+      </c>
+      <c r="F31" s="91"/>
+      <c r="G31" s="110"/>
+      <c r="H31" s="3"/>
+      <c r="I31" s="3"/>
+      <c r="J31" s="3"/>
+      <c r="K31" s="3"/>
+      <c r="L31" s="3"/>
+      <c r="M31" s="3"/>
+      <c r="N31" s="3"/>
+      <c r="O31" s="3"/>
+      <c r="P31" s="3"/>
+      <c r="Q31" s="3"/>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="B32" s="91"/>
+      <c r="C32" s="91"/>
+      <c r="D32" s="68"/>
+      <c r="E32" s="35" t="s">
+        <v>53</v>
+      </c>
+      <c r="F32" s="91"/>
+      <c r="G32" s="110"/>
+      <c r="H32" s="3"/>
+      <c r="I32" s="3"/>
+      <c r="J32" s="3"/>
+      <c r="K32" s="3"/>
+      <c r="L32" s="3"/>
+      <c r="M32" s="3"/>
+      <c r="N32" s="3"/>
+      <c r="O32" s="3"/>
+      <c r="P32" s="3"/>
+      <c r="Q32" s="3"/>
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="B33" s="91"/>
+      <c r="C33" s="91"/>
+      <c r="D33" s="68"/>
+      <c r="E33" s="35" t="s">
+        <v>54</v>
+      </c>
+      <c r="F33" s="91"/>
+      <c r="G33" s="110"/>
+      <c r="H33" s="3"/>
+      <c r="I33" s="3"/>
+      <c r="J33" s="3"/>
+      <c r="K33" s="3"/>
+      <c r="L33" s="3"/>
+      <c r="M33" s="3"/>
+      <c r="N33" s="3"/>
+      <c r="O33" s="3"/>
+      <c r="P33" s="3"/>
+      <c r="Q33" s="3"/>
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="B34" s="91"/>
+      <c r="C34" s="91"/>
+      <c r="D34" s="68"/>
+      <c r="E34" s="35" t="s">
+        <v>55</v>
+      </c>
+      <c r="F34" s="91"/>
+      <c r="G34" s="110"/>
+      <c r="H34" s="3"/>
+      <c r="I34" s="3"/>
+      <c r="J34" s="3"/>
+      <c r="K34" s="3"/>
+      <c r="L34" s="3"/>
+      <c r="M34" s="3"/>
+      <c r="N34" s="3"/>
+      <c r="O34" s="3"/>
+      <c r="P34" s="3"/>
+      <c r="Q34" s="3"/>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="91"/>
+      <c r="C35" s="91"/>
+      <c r="D35" s="68"/>
+      <c r="E35" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="F35" s="91"/>
+      <c r="G35" s="110"/>
+      <c r="H35" s="3"/>
+      <c r="I35" s="3"/>
+      <c r="J35" s="3"/>
+      <c r="K35" s="3"/>
+      <c r="L35" s="3"/>
+      <c r="M35" s="3"/>
+      <c r="N35" s="3"/>
+      <c r="O35" s="3"/>
+      <c r="P35" s="3"/>
+      <c r="Q35" s="3"/>
+      <c r="R35" s="3"/>
+    </row>
+    <row r="36" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="35" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="91"/>
+      <c r="C36" s="91"/>
+      <c r="D36" s="68"/>
+      <c r="E36" s="35" t="s">
+        <v>57</v>
+      </c>
+      <c r="F36" s="91"/>
+      <c r="G36" s="110"/>
+      <c r="H36" s="3"/>
+      <c r="I36" s="3"/>
+      <c r="J36" s="3"/>
+      <c r="K36" s="3"/>
+      <c r="L36" s="3"/>
+      <c r="M36" s="3"/>
+      <c r="N36" s="3"/>
+      <c r="O36" s="3"/>
+      <c r="P36" s="3"/>
+      <c r="Q36" s="3"/>
+      <c r="R36" s="3"/>
+    </row>
+    <row r="37" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="35" t="s">
+        <v>77</v>
+      </c>
+      <c r="B37" s="91"/>
+      <c r="C37" s="91"/>
+      <c r="D37" s="68"/>
+      <c r="E37" s="35" t="s">
+        <v>58</v>
+      </c>
+      <c r="F37" s="91"/>
+      <c r="G37" s="110"/>
+      <c r="H37" s="3"/>
+      <c r="I37" s="3"/>
+      <c r="J37" s="3"/>
+      <c r="K37" s="3"/>
+      <c r="L37" s="3"/>
+      <c r="M37" s="3"/>
+      <c r="N37" s="3"/>
+      <c r="O37" s="3"/>
+      <c r="P37" s="3"/>
+      <c r="Q37" s="3"/>
+      <c r="R37" s="3"/>
+    </row>
+    <row r="38" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="35" t="s">
+        <v>43</v>
+      </c>
+      <c r="B38" s="91"/>
+      <c r="C38" s="91"/>
+      <c r="D38" s="68"/>
+      <c r="E38" s="35" t="s">
+        <v>59</v>
+      </c>
+      <c r="F38" s="91"/>
+      <c r="G38" s="110"/>
+      <c r="H38" s="3"/>
+      <c r="I38" s="3"/>
+      <c r="J38" s="3"/>
+      <c r="K38" s="3"/>
+      <c r="L38" s="3"/>
+      <c r="M38" s="3"/>
+      <c r="N38" s="3"/>
+      <c r="O38" s="3"/>
+      <c r="P38" s="3"/>
+      <c r="Q38" s="3"/>
+      <c r="R38" s="3"/>
+    </row>
+    <row r="39" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="35" t="s">
+        <v>44</v>
+      </c>
+      <c r="B39" s="91"/>
+      <c r="C39" s="91"/>
+      <c r="D39" s="68"/>
+      <c r="E39" s="35" t="s">
+        <v>60</v>
+      </c>
+      <c r="F39" s="91"/>
+      <c r="G39" s="110"/>
+      <c r="H39" s="3"/>
+      <c r="I39" s="3"/>
+      <c r="J39" s="3"/>
+      <c r="K39" s="3"/>
+      <c r="L39" s="3"/>
+      <c r="M39" s="3"/>
+      <c r="N39" s="3"/>
+      <c r="O39" s="3"/>
+      <c r="P39" s="3"/>
+      <c r="Q39" s="3"/>
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="B40" s="91"/>
+      <c r="C40" s="91"/>
+      <c r="D40" s="68"/>
+      <c r="E40" s="35" t="s">
+        <v>61</v>
+      </c>
+      <c r="F40" s="91"/>
+      <c r="G40" s="110"/>
+      <c r="H40" s="3"/>
+      <c r="I40" s="3"/>
+      <c r="J40" s="3"/>
+      <c r="K40" s="3"/>
+      <c r="L40" s="3"/>
+      <c r="M40" s="3"/>
+      <c r="N40" s="3"/>
+      <c r="O40" s="3"/>
+      <c r="P40" s="3"/>
+      <c r="Q40" s="3"/>
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="35" t="s">
+        <v>78</v>
+      </c>
+      <c r="B41" s="91"/>
+      <c r="C41" s="91"/>
+      <c r="D41" s="68"/>
+      <c r="E41" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="F41" s="91"/>
+      <c r="G41" s="110"/>
+      <c r="H41" s="3"/>
+      <c r="I41" s="3"/>
+      <c r="J41" s="3"/>
+      <c r="K41" s="3"/>
+      <c r="L41" s="3"/>
+      <c r="M41" s="3"/>
+      <c r="N41" s="3"/>
+      <c r="O41" s="3"/>
+      <c r="P41" s="3"/>
+      <c r="Q41" s="3"/>
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="77"/>
+      <c r="B42" s="91"/>
+      <c r="C42" s="91"/>
+      <c r="D42" s="68"/>
+      <c r="E42" s="32"/>
+      <c r="F42" s="91"/>
+      <c r="G42" s="110"/>
+      <c r="H42" s="3"/>
+      <c r="I42" s="3"/>
+      <c r="J42" s="3"/>
+      <c r="K42" s="3"/>
+      <c r="L42" s="3"/>
+      <c r="M42" s="3"/>
+      <c r="N42" s="3"/>
+      <c r="O42" s="3"/>
+      <c r="P42" s="3"/>
+      <c r="Q42" s="3"/>
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="77"/>
+      <c r="B43" s="91"/>
+      <c r="C43" s="91"/>
+      <c r="D43" s="68"/>
+      <c r="E43" s="32"/>
+      <c r="F43" s="91"/>
+      <c r="G43" s="110"/>
+      <c r="H43" s="3"/>
+      <c r="I43" s="3"/>
+      <c r="J43" s="3"/>
+      <c r="K43" s="3"/>
+      <c r="L43" s="3"/>
+      <c r="M43" s="3"/>
+      <c r="N43" s="3"/>
+      <c r="O43" s="3"/>
+      <c r="P43" s="3"/>
+      <c r="Q43" s="3"/>
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="113" t="s">
+        <v>8</v>
+      </c>
+      <c r="B44" s="114"/>
+      <c r="C44" s="114"/>
+      <c r="D44" s="25"/>
+      <c r="E44" s="114" t="s">
+        <v>9</v>
+      </c>
+      <c r="F44" s="114"/>
+      <c r="G44" s="129"/>
+      <c r="H44" s="3"/>
+      <c r="I44" s="3"/>
+      <c r="J44" s="3"/>
+      <c r="K44" s="3"/>
+      <c r="L44" s="3"/>
+      <c r="M44" s="3"/>
+      <c r="N44" s="3"/>
+      <c r="O44" s="3"/>
+      <c r="P44" s="3"/>
+      <c r="Q44" s="3"/>
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="1:18" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D45" s="25"/>
+      <c r="E45" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F45" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="G45" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="H45" s="3"/>
+      <c r="I45" s="3"/>
+      <c r="J45" s="3"/>
+      <c r="K45" s="3"/>
+      <c r="L45" s="3"/>
+      <c r="M45" s="3"/>
+      <c r="N45" s="3"/>
+      <c r="O45" s="3"/>
+      <c r="P45" s="3"/>
+      <c r="Q45" s="3"/>
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="1:18" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="35" t="s">
+        <v>63</v>
+      </c>
+      <c r="B46" s="97"/>
+      <c r="C46" s="98"/>
+      <c r="D46" s="78"/>
+      <c r="E46" s="74" t="s">
+        <v>66</v>
+      </c>
+      <c r="F46" s="106"/>
+      <c r="G46" s="107"/>
+      <c r="H46" s="3"/>
+      <c r="I46" s="3"/>
+      <c r="J46" s="3"/>
+      <c r="K46" s="3"/>
+      <c r="L46" s="3"/>
+      <c r="M46" s="3"/>
+      <c r="N46" s="3"/>
+      <c r="O46" s="3"/>
+      <c r="P46" s="3"/>
+      <c r="Q46" s="3"/>
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="1:18" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="35" t="s">
+        <v>79</v>
+      </c>
+      <c r="B47" s="97"/>
+      <c r="C47" s="98"/>
+      <c r="D47" s="78"/>
+      <c r="E47" s="74" t="s">
+        <v>67</v>
+      </c>
+      <c r="F47" s="106"/>
+      <c r="G47" s="107"/>
+      <c r="H47" s="3"/>
+      <c r="I47" s="3"/>
+      <c r="J47" s="3"/>
+      <c r="K47" s="3"/>
+      <c r="L47" s="3"/>
+      <c r="M47" s="3"/>
+      <c r="N47" s="3"/>
+      <c r="O47" s="3"/>
+      <c r="P47" s="3"/>
+      <c r="Q47" s="3"/>
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="1:18" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="74"/>
+      <c r="B48" s="97"/>
+      <c r="C48" s="98"/>
+      <c r="D48" s="73"/>
+      <c r="E48" s="79"/>
+      <c r="F48" s="106"/>
+      <c r="G48" s="107"/>
+      <c r="H48" s="3"/>
+      <c r="I48" s="3"/>
+      <c r="J48" s="3"/>
+      <c r="K48" s="3"/>
+      <c r="L48" s="3"/>
+      <c r="M48" s="3"/>
+      <c r="N48" s="3"/>
+      <c r="O48" s="3"/>
+      <c r="P48" s="3"/>
+      <c r="Q48" s="3"/>
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="1:18" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="80"/>
+      <c r="B49" s="97"/>
+      <c r="C49" s="98"/>
+      <c r="D49" s="73"/>
+      <c r="E49" s="79"/>
+      <c r="F49" s="106"/>
+      <c r="G49" s="107"/>
+      <c r="H49" s="3"/>
+      <c r="I49" s="3"/>
+      <c r="J49" s="3"/>
+      <c r="K49" s="3"/>
+      <c r="L49" s="3"/>
+      <c r="M49" s="3"/>
+      <c r="N49" s="3"/>
+      <c r="O49" s="3"/>
+      <c r="P49" s="3"/>
+      <c r="Q49" s="3"/>
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="1:18" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="80"/>
+      <c r="B50" s="97"/>
+      <c r="C50" s="98"/>
+      <c r="D50" s="73"/>
+      <c r="E50" s="79"/>
+      <c r="F50" s="106"/>
+      <c r="G50" s="107"/>
+      <c r="H50" s="3"/>
+      <c r="I50" s="3"/>
+      <c r="J50" s="3"/>
+      <c r="K50" s="3"/>
+      <c r="L50" s="3"/>
+      <c r="M50" s="3"/>
+      <c r="N50" s="3"/>
+      <c r="O50" s="3"/>
+      <c r="P50" s="3"/>
+      <c r="Q50" s="3"/>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="1:18" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="80"/>
+      <c r="B51" s="97"/>
+      <c r="C51" s="98"/>
+      <c r="D51" s="78"/>
+      <c r="E51" s="74"/>
+      <c r="F51" s="106"/>
+      <c r="G51" s="107"/>
+      <c r="H51" s="3"/>
+      <c r="I51" s="3"/>
+      <c r="J51" s="3"/>
+      <c r="K51" s="3"/>
+      <c r="L51" s="3"/>
+      <c r="M51" s="3"/>
+      <c r="N51" s="3"/>
+      <c r="O51" s="3"/>
+      <c r="P51" s="3"/>
+      <c r="Q51" s="3"/>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="113" t="s">
+        <v>11</v>
+      </c>
+      <c r="B52" s="114"/>
+      <c r="C52" s="114"/>
+      <c r="D52" s="24"/>
+      <c r="E52" s="115" t="s">
+        <v>10</v>
+      </c>
+      <c r="F52" s="116"/>
+      <c r="G52" s="117"/>
+    </row>
+    <row r="53" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="B53" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D53" s="24"/>
+      <c r="E53" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F53" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="G53" s="20" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="35" t="s">
+        <v>64</v>
+      </c>
+      <c r="B54" s="97"/>
+      <c r="C54" s="98"/>
+      <c r="D54" s="73"/>
+      <c r="E54" s="79"/>
+      <c r="F54" s="106"/>
+      <c r="G54" s="107"/>
+    </row>
+    <row r="55" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="35" t="s">
+        <v>65</v>
+      </c>
+      <c r="B55" s="97"/>
+      <c r="C55" s="98"/>
+      <c r="D55" s="73"/>
+      <c r="E55" s="79"/>
+      <c r="F55" s="106"/>
+      <c r="G55" s="107"/>
+    </row>
+    <row r="56" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="80"/>
+      <c r="B56" s="97"/>
+      <c r="C56" s="98"/>
+      <c r="D56" s="81"/>
+      <c r="E56" s="79"/>
+      <c r="F56" s="106"/>
+      <c r="G56" s="107"/>
+    </row>
+    <row r="57" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="82"/>
+      <c r="B57" s="101"/>
+      <c r="C57" s="102"/>
+      <c r="D57" s="81"/>
+      <c r="E57" s="83"/>
+      <c r="F57" s="91"/>
+      <c r="G57" s="110"/>
+    </row>
+    <row r="58" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="82"/>
+      <c r="B58" s="101"/>
+      <c r="C58" s="102"/>
+      <c r="D58" s="81"/>
+      <c r="E58" s="83"/>
+      <c r="F58" s="91"/>
+      <c r="G58" s="110"/>
+    </row>
+    <row r="59" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="82"/>
+      <c r="B59" s="101"/>
+      <c r="C59" s="102"/>
+      <c r="D59" s="81"/>
+      <c r="E59" s="83"/>
+      <c r="F59" s="91"/>
+      <c r="G59" s="110"/>
+    </row>
+    <row r="60" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="82"/>
+      <c r="B60" s="101"/>
+      <c r="C60" s="102"/>
+      <c r="D60" s="81"/>
+      <c r="E60" s="83"/>
+      <c r="F60" s="91"/>
+      <c r="G60" s="110"/>
+    </row>
+    <row r="61" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="82"/>
+      <c r="B61" s="101"/>
+      <c r="C61" s="102"/>
+      <c r="D61" s="81"/>
+      <c r="E61" s="83"/>
+      <c r="F61" s="91"/>
+      <c r="G61" s="110"/>
+    </row>
+    <row r="62" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="82"/>
+      <c r="B62" s="101"/>
+      <c r="C62" s="102"/>
+      <c r="D62" s="81"/>
+      <c r="E62" s="83"/>
+      <c r="F62" s="91"/>
+      <c r="G62" s="110"/>
+    </row>
+    <row r="63" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="82"/>
+      <c r="B63" s="101"/>
+      <c r="C63" s="102"/>
+      <c r="D63" s="81"/>
+      <c r="E63" s="83"/>
+      <c r="F63" s="91"/>
+      <c r="G63" s="110"/>
+    </row>
+    <row r="64" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="82"/>
+      <c r="B64" s="101"/>
+      <c r="C64" s="102"/>
+      <c r="D64" s="81"/>
+      <c r="E64" s="83"/>
+      <c r="F64" s="91"/>
+      <c r="G64" s="110"/>
+    </row>
+    <row r="65" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="82"/>
+      <c r="B65" s="101"/>
+      <c r="C65" s="102"/>
+      <c r="D65" s="85"/>
+      <c r="E65" s="84"/>
+      <c r="F65" s="91"/>
+      <c r="G65" s="110"/>
+    </row>
+    <row r="66" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="82"/>
+      <c r="B66" s="101"/>
+      <c r="C66" s="102"/>
+      <c r="D66" s="85"/>
+      <c r="E66" s="84"/>
+      <c r="F66" s="91"/>
+      <c r="G66" s="110"/>
+    </row>
+    <row r="67" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="82"/>
+      <c r="B67" s="101"/>
+      <c r="C67" s="102"/>
+      <c r="D67" s="85"/>
+      <c r="E67" s="84"/>
+      <c r="F67" s="91"/>
+      <c r="G67" s="110"/>
+    </row>
+    <row r="68" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="82"/>
+      <c r="B68" s="101"/>
+      <c r="C68" s="102"/>
+      <c r="D68" s="86"/>
+      <c r="E68" s="84"/>
+      <c r="F68" s="91"/>
+      <c r="G68" s="110"/>
+    </row>
+    <row r="69" spans="1:7" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="87"/>
+      <c r="B69" s="88"/>
+      <c r="C69" s="88"/>
+      <c r="D69" s="89"/>
+      <c r="E69" s="90"/>
+      <c r="F69" s="111"/>
+      <c r="G69" s="112"/>
+    </row>
+    <row r="70" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="71" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="72" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="73" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="74" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="75" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="76" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="77" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="78" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="79" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="80" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="B1:G1"/>
     <mergeCell ref="A44:C44"/>
     <mergeCell ref="E44:G44"/>
     <mergeCell ref="A52:C52"/>
@@ -3236,10 +6197,869 @@
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="E15:G15"/>
-    <mergeCell ref="B1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.25" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9639885-A565-A84E-992A-A4144FE2AAD2}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E75"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="43.83203125" style="37" customWidth="1"/>
+    <col min="2" max="2" width="22.83203125" style="36" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" style="37"/>
+    <col min="4" max="4" width="46.1640625" style="37" customWidth="1"/>
+    <col min="5" max="5" width="29.6640625" style="36" customWidth="1"/>
+    <col min="6" max="16384" width="10.83203125" style="37"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="104" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="36"/>
+      <c r="B1" s="134" t="s">
+        <v>80</v>
+      </c>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+    </row>
+    <row r="2" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="122" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="122"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="56"/>
+    </row>
+    <row r="3" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="27"/>
+      <c r="D3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="60" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="57">
+        <v>82</v>
+      </c>
+      <c r="C4" s="61"/>
+      <c r="D4" s="60" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="57"/>
+    </row>
+    <row r="5" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="60" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="57">
+        <v>58</v>
+      </c>
+      <c r="C5" s="28"/>
+      <c r="D5" s="60" t="s">
+        <v>70</v>
+      </c>
+      <c r="E5" s="57"/>
+    </row>
+    <row r="6" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="60" t="s">
+        <v>68</v>
+      </c>
+      <c r="B6" s="57">
+        <v>108</v>
+      </c>
+      <c r="C6" s="28"/>
+      <c r="D6" s="60" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="57"/>
+    </row>
+    <row r="7" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="60" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="57">
+        <v>87</v>
+      </c>
+      <c r="C7" s="28"/>
+      <c r="D7" s="60" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="57"/>
+    </row>
+    <row r="8" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="60" t="s">
+        <v>69</v>
+      </c>
+      <c r="B8" s="57">
+        <v>131</v>
+      </c>
+      <c r="C8" s="28"/>
+      <c r="D8" s="60" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="57"/>
+    </row>
+    <row r="9" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="60" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="57">
+        <v>70</v>
+      </c>
+      <c r="C9" s="26"/>
+      <c r="D9" s="60" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" s="57"/>
+    </row>
+    <row r="10" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="60" t="s">
+        <v>83</v>
+      </c>
+      <c r="B10" s="57">
+        <v>96</v>
+      </c>
+      <c r="C10" s="28"/>
+      <c r="D10" s="60" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="57"/>
+    </row>
+    <row r="11" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="60" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="57"/>
+      <c r="C11" s="28"/>
+      <c r="D11" s="60" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" s="57"/>
+    </row>
+    <row r="12" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="60" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="57"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="60" t="s">
+        <v>71</v>
+      </c>
+      <c r="E12" s="57"/>
+    </row>
+    <row r="13" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B13" s="57">
+        <v>87</v>
+      </c>
+      <c r="C13" s="28"/>
+      <c r="D13" s="60" t="s">
+        <v>72</v>
+      </c>
+      <c r="E13" s="57"/>
+    </row>
+    <row r="14" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="B14" s="54">
+        <v>11</v>
+      </c>
+      <c r="C14" s="29"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="57"/>
+    </row>
+    <row r="15" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="135" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" s="136"/>
+      <c r="C15" s="38"/>
+      <c r="D15" s="132" t="s">
+        <v>7</v>
+      </c>
+      <c r="E15" s="133"/>
+    </row>
+    <row r="16" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="39" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="38"/>
+      <c r="D16" s="40" t="s">
+        <v>4</v>
+      </c>
+      <c r="E16" s="41" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="60" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" s="53"/>
+      <c r="C17" s="42"/>
+      <c r="D17" s="60" t="s">
+        <v>32</v>
+      </c>
+      <c r="E17" s="58"/>
+    </row>
+    <row r="18" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="60" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" s="53"/>
+      <c r="C18" s="42"/>
+      <c r="D18" s="60" t="s">
+        <v>33</v>
+      </c>
+      <c r="E18" s="58"/>
+    </row>
+    <row r="19" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="60" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" s="53"/>
+      <c r="C19" s="42"/>
+      <c r="D19" s="60" t="s">
+        <v>34</v>
+      </c>
+      <c r="E19" s="58"/>
+    </row>
+    <row r="20" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="60" t="s">
+        <v>30</v>
+      </c>
+      <c r="B20" s="53"/>
+      <c r="C20" s="42"/>
+      <c r="D20" s="60" t="s">
+        <v>35</v>
+      </c>
+      <c r="E20" s="58"/>
+    </row>
+    <row r="21" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="60" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21" s="54"/>
+      <c r="C21" s="29"/>
+      <c r="D21" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="E21" s="57"/>
+    </row>
+    <row r="22" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="18"/>
+      <c r="B22" s="54"/>
+      <c r="C22" s="29"/>
+      <c r="D22" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="E22" s="57"/>
+    </row>
+    <row r="23" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="21"/>
+      <c r="B23" s="55"/>
+      <c r="C23" s="29"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="59"/>
+    </row>
+    <row r="24" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="137" t="s">
+        <v>12</v>
+      </c>
+      <c r="B24" s="138"/>
+      <c r="C24" s="138"/>
+      <c r="D24" s="138"/>
+      <c r="E24" s="138"/>
+    </row>
+    <row r="25" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="44" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C25" s="46"/>
+      <c r="D25" s="45" t="s">
+        <v>4</v>
+      </c>
+      <c r="E25" s="45" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="60" t="s">
+        <v>90</v>
+      </c>
+      <c r="B26" s="57">
+        <v>9</v>
+      </c>
+      <c r="C26" s="61"/>
+      <c r="D26" s="60" t="s">
+        <v>48</v>
+      </c>
+      <c r="E26" s="57"/>
+    </row>
+    <row r="27" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="60" t="s">
+        <v>91</v>
+      </c>
+      <c r="B27" s="57">
+        <v>4</v>
+      </c>
+      <c r="C27" s="61"/>
+      <c r="D27" s="60" t="s">
+        <v>96</v>
+      </c>
+      <c r="E27" s="57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="60" t="s">
+        <v>92</v>
+      </c>
+      <c r="B28" s="57">
+        <v>5</v>
+      </c>
+      <c r="C28" s="61"/>
+      <c r="D28" s="60" t="s">
+        <v>97</v>
+      </c>
+      <c r="E28" s="57">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="62" t="s">
+        <v>102</v>
+      </c>
+      <c r="B29" s="63">
+        <v>9</v>
+      </c>
+      <c r="C29" s="61"/>
+      <c r="D29" s="60" t="s">
+        <v>98</v>
+      </c>
+      <c r="E29" s="57">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="60" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="57">
+        <v>12</v>
+      </c>
+      <c r="C30" s="61"/>
+      <c r="D30" s="60" t="s">
+        <v>49</v>
+      </c>
+      <c r="E30" s="57"/>
+    </row>
+    <row r="31" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="60" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="57">
+        <v>10</v>
+      </c>
+      <c r="C31" s="61"/>
+      <c r="D31" s="60" t="s">
+        <v>74</v>
+      </c>
+      <c r="E31" s="57"/>
+    </row>
+    <row r="32" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="60" t="s">
+        <v>75</v>
+      </c>
+      <c r="B32" s="57"/>
+      <c r="C32" s="61"/>
+      <c r="D32" s="60" t="s">
+        <v>50</v>
+      </c>
+      <c r="E32" s="57"/>
+    </row>
+    <row r="33" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="B33" s="57">
+        <v>62</v>
+      </c>
+      <c r="C33" s="61"/>
+      <c r="D33" s="60" t="s">
+        <v>51</v>
+      </c>
+      <c r="E33" s="57"/>
+    </row>
+    <row r="34" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="60" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" s="57">
+        <v>12</v>
+      </c>
+      <c r="C34" s="61"/>
+      <c r="D34" s="60" t="s">
+        <v>52</v>
+      </c>
+      <c r="E34" s="57"/>
+    </row>
+    <row r="35" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="60" t="s">
+        <v>40</v>
+      </c>
+      <c r="B35" s="57"/>
+      <c r="C35" s="61"/>
+      <c r="D35" s="60" t="s">
+        <v>53</v>
+      </c>
+      <c r="E35" s="57"/>
+    </row>
+    <row r="36" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="60" t="s">
+        <v>46</v>
+      </c>
+      <c r="B36" s="57"/>
+      <c r="C36" s="61"/>
+      <c r="D36" s="60" t="s">
+        <v>100</v>
+      </c>
+      <c r="E36" s="57">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="60" t="s">
+        <v>99</v>
+      </c>
+      <c r="B37" s="57">
+        <v>4</v>
+      </c>
+      <c r="C37" s="61"/>
+      <c r="D37" s="60" t="s">
+        <v>55</v>
+      </c>
+      <c r="E37" s="57">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="60" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38" s="57"/>
+      <c r="C38" s="61"/>
+      <c r="D38" s="60" t="s">
+        <v>56</v>
+      </c>
+      <c r="E38" s="57"/>
+    </row>
+    <row r="39" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="60" t="s">
+        <v>42</v>
+      </c>
+      <c r="B39" s="57"/>
+      <c r="C39" s="61"/>
+      <c r="D39" s="60" t="s">
+        <v>57</v>
+      </c>
+      <c r="E39" s="57"/>
+    </row>
+    <row r="40" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="60" t="s">
+        <v>77</v>
+      </c>
+      <c r="B40" s="57">
+        <v>9</v>
+      </c>
+      <c r="C40" s="61"/>
+      <c r="D40" s="60" t="s">
+        <v>58</v>
+      </c>
+      <c r="E40" s="57"/>
+    </row>
+    <row r="41" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="60" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41" s="57"/>
+      <c r="C41" s="61"/>
+      <c r="D41" s="60" t="s">
+        <v>87</v>
+      </c>
+      <c r="E41" s="57">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="60" t="s">
+        <v>44</v>
+      </c>
+      <c r="B42" s="57"/>
+      <c r="C42" s="61"/>
+      <c r="D42" s="60" t="s">
+        <v>60</v>
+      </c>
+      <c r="E42" s="57"/>
+    </row>
+    <row r="43" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="60" t="s">
+        <v>45</v>
+      </c>
+      <c r="B43" s="57"/>
+      <c r="C43" s="61"/>
+      <c r="D43" s="60" t="s">
+        <v>61</v>
+      </c>
+      <c r="E43" s="57"/>
+    </row>
+    <row r="44" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="60" t="s">
+        <v>78</v>
+      </c>
+      <c r="B44" s="57"/>
+      <c r="C44" s="61"/>
+      <c r="D44" s="60" t="s">
+        <v>62</v>
+      </c>
+      <c r="E44" s="57"/>
+    </row>
+    <row r="45" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="64" t="s">
+        <v>84</v>
+      </c>
+      <c r="B45" s="57">
+        <v>11</v>
+      </c>
+      <c r="C45" s="61"/>
+      <c r="D45" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="E45" s="57">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="64" t="s">
+        <v>101</v>
+      </c>
+      <c r="B46" s="57">
+        <v>2</v>
+      </c>
+      <c r="C46" s="61"/>
+      <c r="D46" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E46" s="57"/>
+    </row>
+    <row r="47" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="64"/>
+      <c r="B47" s="57"/>
+      <c r="C47" s="61"/>
+      <c r="D47" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="E47" s="57">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="64"/>
+      <c r="B48" s="57"/>
+      <c r="C48" s="61"/>
+      <c r="D48" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="E48" s="57"/>
+    </row>
+    <row r="49" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="64" t="s">
+        <v>85</v>
+      </c>
+      <c r="B49" s="57">
+        <v>12</v>
+      </c>
+      <c r="C49" s="61"/>
+      <c r="D49" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="E49" s="57">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="130" t="s">
+        <v>8</v>
+      </c>
+      <c r="B50" s="131"/>
+      <c r="C50" s="46"/>
+      <c r="D50" s="131" t="s">
+        <v>9</v>
+      </c>
+      <c r="E50" s="131"/>
+    </row>
+    <row r="51" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="39" t="s">
+        <v>4</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C51" s="46"/>
+      <c r="D51" s="41" t="s">
+        <v>4</v>
+      </c>
+      <c r="E51" s="41" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="60" t="s">
+        <v>63</v>
+      </c>
+      <c r="B52" s="53">
+        <v>10</v>
+      </c>
+      <c r="C52" s="47"/>
+      <c r="D52" s="43" t="s">
+        <v>66</v>
+      </c>
+      <c r="E52" s="58">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="60" t="s">
+        <v>86</v>
+      </c>
+      <c r="B53" s="53">
+        <v>5</v>
+      </c>
+      <c r="C53" s="47"/>
+      <c r="D53" s="43" t="s">
+        <v>67</v>
+      </c>
+      <c r="E53" s="58"/>
+    </row>
+    <row r="54" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="60" t="s">
+        <v>79</v>
+      </c>
+      <c r="B54" s="53">
+        <v>4</v>
+      </c>
+      <c r="C54" s="42"/>
+      <c r="D54" s="48"/>
+      <c r="E54" s="58"/>
+    </row>
+    <row r="55" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="49"/>
+      <c r="B55" s="53"/>
+      <c r="C55" s="42"/>
+      <c r="D55" s="48"/>
+      <c r="E55" s="58"/>
+    </row>
+    <row r="56" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="49"/>
+      <c r="B56" s="53"/>
+      <c r="C56" s="42"/>
+      <c r="D56" s="48"/>
+      <c r="E56" s="58"/>
+    </row>
+    <row r="57" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="49"/>
+      <c r="B57" s="53"/>
+      <c r="C57" s="47"/>
+      <c r="D57" s="43"/>
+      <c r="E57" s="58"/>
+    </row>
+    <row r="58" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="130" t="s">
+        <v>11</v>
+      </c>
+      <c r="B58" s="131"/>
+      <c r="C58" s="42"/>
+      <c r="D58" s="132" t="s">
+        <v>10</v>
+      </c>
+      <c r="E58" s="133"/>
+    </row>
+    <row r="59" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="39" t="s">
+        <v>4</v>
+      </c>
+      <c r="B59" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C59" s="42"/>
+      <c r="D59" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="E59" s="41" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="60" t="s">
+        <v>64</v>
+      </c>
+      <c r="B60" s="53"/>
+      <c r="C60" s="42"/>
+      <c r="D60" s="48"/>
+      <c r="E60" s="58"/>
+    </row>
+    <row r="61" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="60" t="s">
+        <v>65</v>
+      </c>
+      <c r="B61" s="53"/>
+      <c r="C61" s="42"/>
+      <c r="D61" s="48"/>
+      <c r="E61" s="58"/>
+    </row>
+    <row r="62" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="49"/>
+      <c r="B62" s="53"/>
+      <c r="C62" s="29"/>
+      <c r="D62" s="48"/>
+      <c r="E62" s="58"/>
+    </row>
+    <row r="63" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="18"/>
+      <c r="B63" s="54"/>
+      <c r="C63" s="29"/>
+      <c r="D63" s="8"/>
+      <c r="E63" s="57"/>
+    </row>
+    <row r="64" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="18"/>
+      <c r="B64" s="54"/>
+      <c r="C64" s="29"/>
+      <c r="D64" s="8"/>
+      <c r="E64" s="57"/>
+    </row>
+    <row r="65" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="18"/>
+      <c r="B65" s="54"/>
+      <c r="C65" s="29"/>
+      <c r="D65" s="8"/>
+      <c r="E65" s="57"/>
+    </row>
+    <row r="66" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="18"/>
+      <c r="B66" s="54"/>
+      <c r="C66" s="29"/>
+      <c r="D66" s="8"/>
+      <c r="E66" s="57"/>
+    </row>
+    <row r="67" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="18"/>
+      <c r="B67" s="54"/>
+      <c r="C67" s="29"/>
+      <c r="D67" s="8"/>
+      <c r="E67" s="57"/>
+    </row>
+    <row r="68" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="18"/>
+      <c r="B68" s="54"/>
+      <c r="C68" s="29"/>
+      <c r="D68" s="8"/>
+      <c r="E68" s="57"/>
+    </row>
+    <row r="69" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="18"/>
+      <c r="B69" s="54"/>
+      <c r="C69" s="29"/>
+      <c r="D69" s="8"/>
+      <c r="E69" s="57"/>
+    </row>
+    <row r="70" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="18"/>
+      <c r="B70" s="54"/>
+      <c r="C70" s="29"/>
+      <c r="D70" s="8"/>
+      <c r="E70" s="57"/>
+    </row>
+    <row r="71" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="18"/>
+      <c r="B71" s="54"/>
+      <c r="C71" s="28"/>
+      <c r="D71" s="5"/>
+      <c r="E71" s="57"/>
+    </row>
+    <row r="72" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="18"/>
+      <c r="B72" s="54"/>
+      <c r="C72" s="28"/>
+      <c r="D72" s="5"/>
+      <c r="E72" s="57"/>
+    </row>
+    <row r="73" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="18"/>
+      <c r="B73" s="54"/>
+      <c r="C73" s="28"/>
+      <c r="D73" s="5"/>
+      <c r="E73" s="57"/>
+    </row>
+    <row r="74" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="18"/>
+      <c r="B74" s="54"/>
+      <c r="C74" s="46"/>
+      <c r="D74" s="5"/>
+      <c r="E74" s="57"/>
+    </row>
+    <row r="75" spans="1:5" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="51"/>
+      <c r="B75" s="52"/>
+      <c r="C75" s="65"/>
+      <c r="D75" s="66"/>
+      <c r="E75" s="67"/>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="D58:E58"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="D50:E50"/>
+  </mergeCells>
+  <printOptions verticalCentered="1"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup scale="37" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/PLATEWARE PULL SHEET - TEMPLATE.xlsx
+++ b/PLATEWARE PULL SHEET - TEMPLATE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/davidcuvin/purveyor_project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91C7CEA0-039B-E74A-BECF-7723CFB13585}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B656501A-E449-1141-A8A6-BAABCB3A52C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="980" windowWidth="29940" windowHeight="17600" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="105">
   <si>
     <t>Event Name:             Event Date:</t>
   </si>
@@ -173,9 +173,6 @@
     <t>White 3 Tier</t>
   </si>
   <si>
-    <t>Silver 2 Tier</t>
-  </si>
-  <si>
     <t>French Onion Bowl</t>
   </si>
   <si>
@@ -342,6 +339,12 @@
   </si>
   <si>
     <t>Shot Glass</t>
+  </si>
+  <si>
+    <t>French Fry Cups</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 Cuped Metal Rammekins </t>
   </si>
 </sst>
 </file>
@@ -1216,12 +1219,36 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1231,18 +1258,6 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1254,18 +1269,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1789,14 +1792,14 @@
   <sheetData>
     <row r="1" spans="1:15" ht="60.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="31"/>
-      <c r="B1" s="118" t="s">
+      <c r="B1" s="113" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="119"/>
-      <c r="D1" s="120"/>
-      <c r="E1" s="120"/>
-      <c r="F1" s="120"/>
-      <c r="G1" s="121"/>
+      <c r="C1" s="114"/>
+      <c r="D1" s="115"/>
+      <c r="E1" s="115"/>
+      <c r="F1" s="115"/>
+      <c r="G1" s="116"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
@@ -1807,11 +1810,11 @@
       <c r="O1" s="1"/>
     </row>
     <row r="2" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="122" t="s">
+      <c r="A2" s="126" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="122"/>
-      <c r="C2" s="122"/>
+      <c r="B2" s="126"/>
+      <c r="C2" s="126"/>
       <c r="D2" s="26"/>
       <c r="E2" s="15" t="s">
         <v>5</v>
@@ -2044,17 +2047,17 @@
       <c r="O14" s="3"/>
     </row>
     <row r="15" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="123" t="s">
+      <c r="A15" s="127" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="124"/>
-      <c r="C15" s="125"/>
+      <c r="B15" s="128"/>
+      <c r="C15" s="129"/>
       <c r="D15" s="30"/>
-      <c r="E15" s="115" t="s">
+      <c r="E15" s="123" t="s">
         <v>7</v>
       </c>
-      <c r="F15" s="116"/>
-      <c r="G15" s="117"/>
+      <c r="F15" s="124"/>
+      <c r="G15" s="125"/>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
       <c r="J15" s="3"/>
@@ -2213,15 +2216,15 @@
       <c r="O23" s="3"/>
     </row>
     <row r="24" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="126" t="s">
+      <c r="A24" s="120" t="s">
         <v>12</v>
       </c>
-      <c r="B24" s="127"/>
-      <c r="C24" s="127"/>
-      <c r="D24" s="127"/>
-      <c r="E24" s="127"/>
-      <c r="F24" s="127"/>
-      <c r="G24" s="128"/>
+      <c r="B24" s="121"/>
+      <c r="C24" s="121"/>
+      <c r="D24" s="121"/>
+      <c r="E24" s="121"/>
+      <c r="F24" s="121"/>
+      <c r="G24" s="122"/>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
       <c r="J24" s="3"/>
@@ -2627,17 +2630,17 @@
       <c r="R43" s="3"/>
     </row>
     <row r="44" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="113" t="s">
+      <c r="A44" s="117" t="s">
         <v>8</v>
       </c>
-      <c r="B44" s="114"/>
-      <c r="C44" s="114"/>
+      <c r="B44" s="118"/>
+      <c r="C44" s="118"/>
       <c r="D44" s="25"/>
-      <c r="E44" s="114" t="s">
+      <c r="E44" s="118" t="s">
         <v>9</v>
       </c>
-      <c r="F44" s="114"/>
-      <c r="G44" s="129"/>
+      <c r="F44" s="118"/>
+      <c r="G44" s="119"/>
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>
       <c r="J44" s="3"/>
@@ -2803,17 +2806,17 @@
       <c r="R51" s="3"/>
     </row>
     <row r="52" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="113" t="s">
+      <c r="A52" s="117" t="s">
         <v>11</v>
       </c>
-      <c r="B52" s="114"/>
-      <c r="C52" s="114"/>
+      <c r="B52" s="118"/>
+      <c r="C52" s="118"/>
       <c r="D52" s="24"/>
-      <c r="E52" s="115" t="s">
+      <c r="E52" s="123" t="s">
         <v>10</v>
       </c>
-      <c r="F52" s="116"/>
-      <c r="G52" s="117"/>
+      <c r="F52" s="124"/>
+      <c r="G52" s="125"/>
     </row>
     <row r="53" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="19" t="s">
@@ -3941,14 +3944,14 @@
   <sheetData>
     <row r="1" spans="1:15" ht="60.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="31"/>
-      <c r="B1" s="118" t="s">
+      <c r="B1" s="113" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="119"/>
-      <c r="D1" s="120"/>
-      <c r="E1" s="120"/>
-      <c r="F1" s="120"/>
-      <c r="G1" s="121"/>
+      <c r="C1" s="114"/>
+      <c r="D1" s="115"/>
+      <c r="E1" s="115"/>
+      <c r="F1" s="115"/>
+      <c r="G1" s="116"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
@@ -3959,11 +3962,11 @@
       <c r="O1" s="1"/>
     </row>
     <row r="2" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="122" t="s">
+      <c r="A2" s="126" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="122"/>
-      <c r="C2" s="122"/>
+      <c r="B2" s="126"/>
+      <c r="C2" s="126"/>
       <c r="D2" s="26"/>
       <c r="E2" s="15" t="s">
         <v>5</v>
@@ -4037,7 +4040,7 @@
       <c r="C5" s="93"/>
       <c r="D5" s="69"/>
       <c r="E5" s="35" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F5" s="92"/>
       <c r="G5" s="105"/>
@@ -4052,7 +4055,7 @@
     </row>
     <row r="6" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="35" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B6" s="92"/>
       <c r="C6" s="93"/>
@@ -4094,7 +4097,7 @@
     </row>
     <row r="8" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="35" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B8" s="92"/>
       <c r="C8" s="93"/>
@@ -4184,7 +4187,7 @@
       <c r="C12" s="93"/>
       <c r="D12" s="69"/>
       <c r="E12" s="35" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F12" s="92"/>
       <c r="G12" s="105"/>
@@ -4203,7 +4206,7 @@
       <c r="C13" s="93"/>
       <c r="D13" s="69"/>
       <c r="E13" s="35" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F13" s="92"/>
       <c r="G13" s="105"/>
@@ -4234,17 +4237,17 @@
       <c r="O14" s="3"/>
     </row>
     <row r="15" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="123" t="s">
+      <c r="A15" s="127" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="124"/>
-      <c r="C15" s="125"/>
+      <c r="B15" s="128"/>
+      <c r="C15" s="129"/>
       <c r="D15" s="30"/>
-      <c r="E15" s="115" t="s">
+      <c r="E15" s="123" t="s">
         <v>7</v>
       </c>
-      <c r="F15" s="116"/>
-      <c r="G15" s="117"/>
+      <c r="F15" s="124"/>
+      <c r="G15" s="125"/>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
       <c r="J15" s="3"/>
@@ -4423,15 +4426,15 @@
       <c r="O23" s="3"/>
     </row>
     <row r="24" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="126" t="s">
+      <c r="A24" s="120" t="s">
         <v>12</v>
       </c>
-      <c r="B24" s="127"/>
-      <c r="C24" s="127"/>
-      <c r="D24" s="127"/>
-      <c r="E24" s="127"/>
-      <c r="F24" s="127"/>
-      <c r="G24" s="128"/>
+      <c r="B24" s="121"/>
+      <c r="C24" s="121"/>
+      <c r="D24" s="121"/>
+      <c r="E24" s="121"/>
+      <c r="F24" s="121"/>
+      <c r="G24" s="122"/>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
       <c r="J24" s="3"/>
@@ -4478,13 +4481,13 @@
     </row>
     <row r="26" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="35" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B26" s="91"/>
       <c r="C26" s="91"/>
       <c r="D26" s="68"/>
       <c r="E26" s="35" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F26" s="91"/>
       <c r="G26" s="110"/>
@@ -4508,7 +4511,7 @@
       <c r="C27" s="91"/>
       <c r="D27" s="68"/>
       <c r="E27" s="35" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F27" s="91"/>
       <c r="G27" s="110"/>
@@ -4532,7 +4535,7 @@
       <c r="C28" s="91"/>
       <c r="D28" s="68"/>
       <c r="E28" s="35" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F28" s="91"/>
       <c r="G28" s="110"/>
@@ -4550,13 +4553,13 @@
     </row>
     <row r="29" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="35" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B29" s="91"/>
       <c r="C29" s="91"/>
       <c r="D29" s="68"/>
       <c r="E29" s="35" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F29" s="91"/>
       <c r="G29" s="110"/>
@@ -4574,13 +4577,13 @@
     </row>
     <row r="30" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="35" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B30" s="91"/>
       <c r="C30" s="91"/>
       <c r="D30" s="68"/>
       <c r="E30" s="35" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F30" s="91"/>
       <c r="G30" s="110"/>
@@ -4604,7 +4607,7 @@
       <c r="C31" s="91"/>
       <c r="D31" s="68"/>
       <c r="E31" s="35" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F31" s="91"/>
       <c r="G31" s="110"/>
@@ -4628,7 +4631,7 @@
       <c r="C32" s="91"/>
       <c r="D32" s="68"/>
       <c r="E32" s="35" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F32" s="91"/>
       <c r="G32" s="110"/>
@@ -4652,7 +4655,7 @@
       <c r="C33" s="91"/>
       <c r="D33" s="68"/>
       <c r="E33" s="35" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F33" s="91"/>
       <c r="G33" s="110"/>
@@ -4670,13 +4673,13 @@
     </row>
     <row r="34" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="35" t="s">
-        <v>47</v>
+        <v>98</v>
       </c>
       <c r="B34" s="91"/>
       <c r="C34" s="91"/>
       <c r="D34" s="68"/>
       <c r="E34" s="35" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F34" s="91"/>
       <c r="G34" s="110"/>
@@ -4700,7 +4703,7 @@
       <c r="C35" s="91"/>
       <c r="D35" s="68"/>
       <c r="E35" s="35" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F35" s="91"/>
       <c r="G35" s="110"/>
@@ -4724,7 +4727,7 @@
       <c r="C36" s="91"/>
       <c r="D36" s="68"/>
       <c r="E36" s="35" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F36" s="91"/>
       <c r="G36" s="110"/>
@@ -4742,13 +4745,13 @@
     </row>
     <row r="37" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="35" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B37" s="91"/>
       <c r="C37" s="91"/>
       <c r="D37" s="68"/>
       <c r="E37" s="35" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F37" s="91"/>
       <c r="G37" s="110"/>
@@ -4772,7 +4775,7 @@
       <c r="C38" s="91"/>
       <c r="D38" s="68"/>
       <c r="E38" s="35" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F38" s="91"/>
       <c r="G38" s="110"/>
@@ -4796,7 +4799,7 @@
       <c r="C39" s="91"/>
       <c r="D39" s="68"/>
       <c r="E39" s="35" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F39" s="91"/>
       <c r="G39" s="110"/>
@@ -4820,7 +4823,7 @@
       <c r="C40" s="91"/>
       <c r="D40" s="68"/>
       <c r="E40" s="35" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F40" s="91"/>
       <c r="G40" s="110"/>
@@ -4838,13 +4841,13 @@
     </row>
     <row r="41" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="35" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B41" s="91"/>
       <c r="C41" s="91"/>
       <c r="D41" s="68"/>
       <c r="E41" s="35" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F41" s="91"/>
       <c r="G41" s="110"/>
@@ -4861,11 +4864,15 @@
       <c r="R41" s="3"/>
     </row>
     <row r="42" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="77"/>
+      <c r="A42" s="77" t="s">
+        <v>103</v>
+      </c>
       <c r="B42" s="91"/>
       <c r="C42" s="91"/>
       <c r="D42" s="68"/>
-      <c r="E42" s="32"/>
+      <c r="E42" s="32" t="s">
+        <v>104</v>
+      </c>
       <c r="F42" s="91"/>
       <c r="G42" s="110"/>
       <c r="H42" s="3"/>
@@ -4901,17 +4908,17 @@
       <c r="R43" s="3"/>
     </row>
     <row r="44" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="113" t="s">
+      <c r="A44" s="117" t="s">
         <v>8</v>
       </c>
-      <c r="B44" s="114"/>
-      <c r="C44" s="114"/>
+      <c r="B44" s="118"/>
+      <c r="C44" s="118"/>
       <c r="D44" s="25"/>
-      <c r="E44" s="114" t="s">
+      <c r="E44" s="118" t="s">
         <v>9</v>
       </c>
-      <c r="F44" s="114"/>
-      <c r="G44" s="129"/>
+      <c r="F44" s="118"/>
+      <c r="G44" s="119"/>
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>
       <c r="J44" s="3"/>
@@ -4958,13 +4965,13 @@
     </row>
     <row r="46" spans="1:18" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="35" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B46" s="97"/>
       <c r="C46" s="98"/>
       <c r="D46" s="78"/>
       <c r="E46" s="74" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F46" s="106"/>
       <c r="G46" s="107"/>
@@ -4982,13 +4989,13 @@
     </row>
     <row r="47" spans="1:18" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="35" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B47" s="97"/>
       <c r="C47" s="98"/>
       <c r="D47" s="78"/>
       <c r="E47" s="74" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F47" s="106"/>
       <c r="G47" s="107"/>
@@ -5085,17 +5092,17 @@
       <c r="R51" s="3"/>
     </row>
     <row r="52" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="113" t="s">
+      <c r="A52" s="117" t="s">
         <v>11</v>
       </c>
-      <c r="B52" s="114"/>
-      <c r="C52" s="114"/>
+      <c r="B52" s="118"/>
+      <c r="C52" s="118"/>
       <c r="D52" s="24"/>
-      <c r="E52" s="115" t="s">
+      <c r="E52" s="123" t="s">
         <v>10</v>
       </c>
-      <c r="F52" s="116"/>
-      <c r="G52" s="117"/>
+      <c r="F52" s="124"/>
+      <c r="G52" s="125"/>
     </row>
     <row r="53" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="19" t="s">
@@ -5120,7 +5127,7 @@
     </row>
     <row r="54" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="35" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B54" s="97"/>
       <c r="C54" s="98"/>
@@ -5131,7 +5138,7 @@
     </row>
     <row r="55" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="35" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B55" s="97"/>
       <c r="C55" s="98"/>
@@ -6223,17 +6230,17 @@
     <row r="1" spans="1:5" ht="104" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="36"/>
       <c r="B1" s="134" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C1" s="134"/>
       <c r="D1" s="134"/>
       <c r="E1" s="134"/>
     </row>
     <row r="2" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="122" t="s">
+      <c r="A2" s="126" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="122"/>
+      <c r="B2" s="126"/>
       <c r="C2" s="26"/>
       <c r="D2" s="15" t="s">
         <v>5</v>
@@ -6277,13 +6284,13 @@
       </c>
       <c r="C5" s="28"/>
       <c r="D5" s="60" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E5" s="57"/>
     </row>
     <row r="6" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="60" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B6" s="57">
         <v>108</v>
@@ -6309,7 +6316,7 @@
     </row>
     <row r="8" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="60" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B8" s="57">
         <v>131</v>
@@ -6335,7 +6342,7 @@
     </row>
     <row r="10" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="60" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B10" s="57">
         <v>96</v>
@@ -6364,26 +6371,26 @@
       <c r="B12" s="57"/>
       <c r="C12" s="28"/>
       <c r="D12" s="60" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E12" s="57"/>
     </row>
     <row r="13" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B13" s="57">
         <v>87</v>
       </c>
       <c r="C13" s="28"/>
       <c r="D13" s="60" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E13" s="57"/>
     </row>
     <row r="14" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="18" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B14" s="54">
         <v>11</v>
@@ -6478,7 +6485,7 @@
       <c r="B22" s="54"/>
       <c r="C22" s="29"/>
       <c r="D22" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E22" s="57"/>
     </row>
@@ -6515,27 +6522,27 @@
     </row>
     <row r="26" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="60" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B26" s="57">
         <v>9</v>
       </c>
       <c r="C26" s="61"/>
       <c r="D26" s="60" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E26" s="57"/>
     </row>
     <row r="27" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="60" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B27" s="57">
         <v>4</v>
       </c>
       <c r="C27" s="61"/>
       <c r="D27" s="60" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E27" s="57">
         <v>1</v>
@@ -6543,14 +6550,14 @@
     </row>
     <row r="28" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="60" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B28" s="57">
         <v>5</v>
       </c>
       <c r="C28" s="61"/>
       <c r="D28" s="60" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E28" s="57">
         <v>2</v>
@@ -6558,14 +6565,14 @@
     </row>
     <row r="29" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="62" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B29" s="63">
         <v>9</v>
       </c>
       <c r="C29" s="61"/>
       <c r="D29" s="60" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E29" s="57">
         <v>3</v>
@@ -6580,7 +6587,7 @@
       </c>
       <c r="C30" s="61"/>
       <c r="D30" s="60" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E30" s="57"/>
     </row>
@@ -6593,31 +6600,31 @@
       </c>
       <c r="C31" s="61"/>
       <c r="D31" s="60" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E31" s="57"/>
     </row>
     <row r="32" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="60" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B32" s="57"/>
       <c r="C32" s="61"/>
       <c r="D32" s="60" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E32" s="57"/>
     </row>
     <row r="33" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="60" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B33" s="57">
         <v>62</v>
       </c>
       <c r="C33" s="61"/>
       <c r="D33" s="60" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E33" s="57"/>
     </row>
@@ -6630,7 +6637,7 @@
       </c>
       <c r="C34" s="61"/>
       <c r="D34" s="60" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E34" s="57"/>
     </row>
@@ -6641,7 +6648,7 @@
       <c r="B35" s="57"/>
       <c r="C35" s="61"/>
       <c r="D35" s="60" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E35" s="57"/>
     </row>
@@ -6652,7 +6659,7 @@
       <c r="B36" s="57"/>
       <c r="C36" s="61"/>
       <c r="D36" s="60" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E36" s="57">
         <v>5</v>
@@ -6660,14 +6667,14 @@
     </row>
     <row r="37" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="60" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B37" s="57">
         <v>4</v>
       </c>
       <c r="C37" s="61"/>
       <c r="D37" s="60" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E37" s="57">
         <v>5</v>
@@ -6680,7 +6687,7 @@
       <c r="B38" s="57"/>
       <c r="C38" s="61"/>
       <c r="D38" s="60" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E38" s="57"/>
     </row>
@@ -6691,20 +6698,20 @@
       <c r="B39" s="57"/>
       <c r="C39" s="61"/>
       <c r="D39" s="60" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E39" s="57"/>
     </row>
     <row r="40" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="60" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B40" s="57">
         <v>9</v>
       </c>
       <c r="C40" s="61"/>
       <c r="D40" s="60" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E40" s="57"/>
     </row>
@@ -6715,7 +6722,7 @@
       <c r="B41" s="57"/>
       <c r="C41" s="61"/>
       <c r="D41" s="60" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E41" s="57">
         <v>3</v>
@@ -6728,7 +6735,7 @@
       <c r="B42" s="57"/>
       <c r="C42" s="61"/>
       <c r="D42" s="60" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E42" s="57"/>
     </row>
@@ -6739,31 +6746,31 @@
       <c r="B43" s="57"/>
       <c r="C43" s="61"/>
       <c r="D43" s="60" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E43" s="57"/>
     </row>
     <row r="44" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="60" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B44" s="57"/>
       <c r="C44" s="61"/>
       <c r="D44" s="60" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E44" s="57"/>
     </row>
     <row r="45" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="64" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B45" s="57">
         <v>11</v>
       </c>
       <c r="C45" s="61"/>
       <c r="D45" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E45" s="57">
         <v>18</v>
@@ -6771,14 +6778,14 @@
     </row>
     <row r="46" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="64" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B46" s="57">
         <v>2</v>
       </c>
       <c r="C46" s="61"/>
       <c r="D46" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E46" s="57"/>
     </row>
@@ -6787,7 +6794,7 @@
       <c r="B47" s="57"/>
       <c r="C47" s="61"/>
       <c r="D47" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E47" s="57">
         <v>6</v>
@@ -6798,20 +6805,20 @@
       <c r="B48" s="57"/>
       <c r="C48" s="61"/>
       <c r="D48" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E48" s="57"/>
     </row>
     <row r="49" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="64" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B49" s="57">
         <v>12</v>
       </c>
       <c r="C49" s="61"/>
       <c r="D49" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E49" s="57">
         <v>13</v>
@@ -6845,14 +6852,14 @@
     </row>
     <row r="52" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="60" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B52" s="53">
         <v>10</v>
       </c>
       <c r="C52" s="47"/>
       <c r="D52" s="43" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E52" s="58">
         <v>25</v>
@@ -6860,20 +6867,20 @@
     </row>
     <row r="53" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="60" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B53" s="53">
         <v>5</v>
       </c>
       <c r="C53" s="47"/>
       <c r="D53" s="43" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E53" s="58"/>
     </row>
     <row r="54" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="60" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B54" s="53">
         <v>4</v>
@@ -6931,7 +6938,7 @@
     </row>
     <row r="60" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="60" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B60" s="53"/>
       <c r="C60" s="42"/>
@@ -6940,7 +6947,7 @@
     </row>
     <row r="61" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="60" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B61" s="53"/>
       <c r="C61" s="42"/>

--- a/PLATEWARE PULL SHEET - TEMPLATE.xlsx
+++ b/PLATEWARE PULL SHEET - TEMPLATE.xlsx
@@ -1,24 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/davidcuvin/purveyor_project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B656501A-E449-1141-A8A6-BAABCB3A52C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0DBE1ED-FF99-6344-A62D-29609AB815AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="980" windowWidth="29940" windowHeight="17600" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="300" yWindow="1200" windowWidth="29940" windowHeight="17600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Updated_Pull_Sheet" sheetId="3" r:id="rId1"/>
-    <sheet name="Pull_Sheet" sheetId="1" r:id="rId2"/>
-    <sheet name="Inventory" sheetId="2" r:id="rId3"/>
+    <sheet name="Pull_Sheet" sheetId="1" r:id="rId1"/>
+    <sheet name="Inventory" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">Inventory!$A$1:$E$75</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">Inventory!$A$1:$E$75</definedName>
   </definedNames>
   <calcPr calcId="0"/>
   <extLst>
@@ -30,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="110">
   <si>
     <t>Event Name:             Event Date:</t>
   </si>
@@ -345,6 +344,21 @@
   </si>
   <si>
     <t xml:space="preserve">3 Cuped Metal Rammekins </t>
+  </si>
+  <si>
+    <t>Large Metal Coupe</t>
+  </si>
+  <si>
+    <t>Medium Metal Coupe</t>
+  </si>
+  <si>
+    <t>Small Metal Coupe</t>
+  </si>
+  <si>
+    <t>Small IRD Tray Paper</t>
+  </si>
+  <si>
+    <t>Lrg IRD Tray Paper</t>
   </si>
 </sst>
 </file>
@@ -879,7 +893,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="139">
+  <cellXfs count="140">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1296,6 +1310,9 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1315,133 +1332,6 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>838200</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>63500</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>1460500</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>660400</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7DD4E620-90CC-884F-9589-33F501A03614}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="838200" y="63500"/>
-          <a:ext cx="622300" cy="596900"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>838200</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>63500</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>1460500</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>660400</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{66C148C2-F6AB-2C47-A272-E40DA007DA99}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="838200" y="63500"/>
-          <a:ext cx="622300" cy="596900"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1507,7 +1397,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1770,11 +1660,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7283AA4-07FC-BE4E-A014-7B45B56A06CA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R989"/>
+  <dimension ref="A1:R991"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="30.5" style="2" customWidth="1"/>
@@ -1860,11 +1750,15 @@
       <c r="O3" s="3"/>
     </row>
     <row r="4" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="35"/>
+      <c r="A4" s="35" t="s">
+        <v>13</v>
+      </c>
       <c r="B4" s="91"/>
       <c r="C4" s="91"/>
       <c r="D4" s="68"/>
-      <c r="E4" s="35"/>
+      <c r="E4" s="35" t="s">
+        <v>17</v>
+      </c>
       <c r="F4" s="92"/>
       <c r="G4" s="105"/>
       <c r="H4" s="3"/>
@@ -1877,11 +1771,15 @@
       <c r="O4" s="3"/>
     </row>
     <row r="5" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="35"/>
+      <c r="A5" s="35" t="s">
+        <v>14</v>
+      </c>
       <c r="B5" s="92"/>
       <c r="C5" s="93"/>
       <c r="D5" s="69"/>
-      <c r="E5" s="35"/>
+      <c r="E5" s="35" t="s">
+        <v>69</v>
+      </c>
       <c r="F5" s="92"/>
       <c r="G5" s="105"/>
       <c r="H5" s="3"/>
@@ -1894,11 +1792,15 @@
       <c r="O5" s="3"/>
     </row>
     <row r="6" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="35"/>
+      <c r="A6" s="35" t="s">
+        <v>67</v>
+      </c>
       <c r="B6" s="92"/>
       <c r="C6" s="93"/>
       <c r="D6" s="69"/>
-      <c r="E6" s="35"/>
+      <c r="E6" s="35" t="s">
+        <v>18</v>
+      </c>
       <c r="F6" s="92"/>
       <c r="G6" s="105"/>
       <c r="H6" s="3"/>
@@ -1911,11 +1813,15 @@
       <c r="O6" s="3"/>
     </row>
     <row r="7" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="35"/>
+      <c r="A7" s="35" t="s">
+        <v>15</v>
+      </c>
       <c r="B7" s="92"/>
       <c r="C7" s="93"/>
       <c r="D7" s="69"/>
-      <c r="E7" s="35"/>
+      <c r="E7" s="35" t="s">
+        <v>19</v>
+      </c>
       <c r="F7" s="92"/>
       <c r="G7" s="105"/>
       <c r="H7" s="3"/>
@@ -1928,11 +1834,15 @@
       <c r="O7" s="3"/>
     </row>
     <row r="8" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="35"/>
+      <c r="A8" s="35" t="s">
+        <v>68</v>
+      </c>
       <c r="B8" s="92"/>
       <c r="C8" s="93"/>
       <c r="D8" s="69"/>
-      <c r="E8" s="35"/>
+      <c r="E8" s="35" t="s">
+        <v>20</v>
+      </c>
       <c r="F8" s="92"/>
       <c r="G8" s="105"/>
       <c r="H8" s="3"/>
@@ -1945,11 +1855,15 @@
       <c r="O8" s="3"/>
     </row>
     <row r="9" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="35"/>
+      <c r="A9" s="35" t="s">
+        <v>16</v>
+      </c>
       <c r="B9" s="94"/>
       <c r="C9" s="95"/>
       <c r="D9" s="70"/>
-      <c r="E9" s="35"/>
+      <c r="E9" s="35" t="s">
+        <v>21</v>
+      </c>
       <c r="F9" s="92"/>
       <c r="G9" s="105"/>
       <c r="H9" s="3"/>
@@ -1962,11 +1876,15 @@
       <c r="O9" s="3"/>
     </row>
     <row r="10" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="35"/>
+      <c r="A10" s="35" t="s">
+        <v>24</v>
+      </c>
       <c r="B10" s="92"/>
       <c r="C10" s="93"/>
       <c r="D10" s="69"/>
-      <c r="E10" s="35"/>
+      <c r="E10" s="35" t="s">
+        <v>22</v>
+      </c>
       <c r="F10" s="92"/>
       <c r="G10" s="105"/>
       <c r="H10" s="3"/>
@@ -1979,11 +1897,15 @@
       <c r="O10" s="3"/>
     </row>
     <row r="11" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="35"/>
+      <c r="A11" s="35" t="s">
+        <v>25</v>
+      </c>
       <c r="B11" s="92"/>
       <c r="C11" s="93"/>
       <c r="D11" s="69"/>
-      <c r="E11" s="35"/>
+      <c r="E11" s="35" t="s">
+        <v>23</v>
+      </c>
       <c r="F11" s="92"/>
       <c r="G11" s="105"/>
       <c r="H11" s="3"/>
@@ -1996,11 +1918,15 @@
       <c r="O11" s="3"/>
     </row>
     <row r="12" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="35"/>
+      <c r="A12" s="35" t="s">
+        <v>26</v>
+      </c>
       <c r="B12" s="92"/>
       <c r="C12" s="93"/>
       <c r="D12" s="69"/>
-      <c r="E12" s="35"/>
+      <c r="E12" s="35" t="s">
+        <v>70</v>
+      </c>
       <c r="F12" s="92"/>
       <c r="G12" s="105"/>
       <c r="H12" s="3"/>
@@ -2017,7 +1943,9 @@
       <c r="B13" s="92"/>
       <c r="C13" s="93"/>
       <c r="D13" s="69"/>
-      <c r="E13" s="35"/>
+      <c r="E13" s="35" t="s">
+        <v>71</v>
+      </c>
       <c r="F13" s="92"/>
       <c r="G13" s="105"/>
       <c r="H13" s="3"/>
@@ -2097,11 +2025,15 @@
       <c r="O16" s="3"/>
     </row>
     <row r="17" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="35"/>
+      <c r="A17" s="35" t="s">
+        <v>27</v>
+      </c>
       <c r="B17" s="97"/>
       <c r="C17" s="98"/>
       <c r="D17" s="73"/>
-      <c r="E17" s="35"/>
+      <c r="E17" s="35" t="s">
+        <v>32</v>
+      </c>
       <c r="F17" s="106"/>
       <c r="G17" s="107"/>
       <c r="H17" s="3"/>
@@ -2114,11 +2046,15 @@
       <c r="O17" s="3"/>
     </row>
     <row r="18" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="35"/>
+      <c r="A18" s="35" t="s">
+        <v>28</v>
+      </c>
       <c r="B18" s="97"/>
       <c r="C18" s="98"/>
       <c r="D18" s="73"/>
-      <c r="E18" s="35"/>
+      <c r="E18" s="35" t="s">
+        <v>33</v>
+      </c>
       <c r="F18" s="106"/>
       <c r="G18" s="107"/>
       <c r="H18" s="3"/>
@@ -2131,11 +2067,15 @@
       <c r="O18" s="3"/>
     </row>
     <row r="19" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="35"/>
+      <c r="A19" s="35" t="s">
+        <v>29</v>
+      </c>
       <c r="B19" s="97"/>
       <c r="C19" s="98"/>
       <c r="D19" s="73"/>
-      <c r="E19" s="35"/>
+      <c r="E19" s="35" t="s">
+        <v>34</v>
+      </c>
       <c r="F19" s="106"/>
       <c r="G19" s="107"/>
       <c r="H19" s="3"/>
@@ -2148,11 +2088,15 @@
       <c r="O19" s="3"/>
     </row>
     <row r="20" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="35"/>
+      <c r="A20" s="35" t="s">
+        <v>30</v>
+      </c>
       <c r="B20" s="97"/>
       <c r="C20" s="98"/>
       <c r="D20" s="73"/>
-      <c r="E20" s="35"/>
+      <c r="E20" s="35" t="s">
+        <v>35</v>
+      </c>
       <c r="F20" s="106"/>
       <c r="G20" s="107"/>
       <c r="H20" s="3"/>
@@ -2165,11 +2109,15 @@
       <c r="O20" s="3"/>
     </row>
     <row r="21" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="35"/>
+      <c r="A21" s="35" t="s">
+        <v>31</v>
+      </c>
       <c r="B21" s="96"/>
       <c r="C21" s="93"/>
       <c r="D21" s="71"/>
-      <c r="E21" s="35"/>
+      <c r="E21" s="35" t="s">
+        <v>36</v>
+      </c>
       <c r="F21" s="92"/>
       <c r="G21" s="105"/>
       <c r="H21" s="3"/>
@@ -2270,11 +2218,15 @@
       <c r="R25" s="3"/>
     </row>
     <row r="26" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="35"/>
+      <c r="A26" s="35" t="s">
+        <v>72</v>
+      </c>
       <c r="B26" s="91"/>
       <c r="C26" s="91"/>
       <c r="D26" s="68"/>
-      <c r="E26" s="35"/>
+      <c r="E26" s="35" t="s">
+        <v>47</v>
+      </c>
       <c r="F26" s="91"/>
       <c r="G26" s="110"/>
       <c r="H26" s="3"/>
@@ -2290,11 +2242,15 @@
       <c r="R26" s="3"/>
     </row>
     <row r="27" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="35"/>
+      <c r="A27" s="35" t="s">
+        <v>37</v>
+      </c>
       <c r="B27" s="91"/>
       <c r="C27" s="91"/>
       <c r="D27" s="68"/>
-      <c r="E27" s="35"/>
+      <c r="E27" s="35" t="s">
+        <v>48</v>
+      </c>
       <c r="F27" s="91"/>
       <c r="G27" s="110"/>
       <c r="H27" s="3"/>
@@ -2310,11 +2266,15 @@
       <c r="R27" s="3"/>
     </row>
     <row r="28" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="35"/>
+      <c r="A28" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="B28" s="91"/>
       <c r="C28" s="91"/>
       <c r="D28" s="68"/>
-      <c r="E28" s="35"/>
+      <c r="E28" s="35" t="s">
+        <v>73</v>
+      </c>
       <c r="F28" s="91"/>
       <c r="G28" s="110"/>
       <c r="H28" s="3"/>
@@ -2330,11 +2290,15 @@
       <c r="R28" s="3"/>
     </row>
     <row r="29" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="35"/>
+      <c r="A29" s="35" t="s">
+        <v>74</v>
+      </c>
       <c r="B29" s="91"/>
       <c r="C29" s="91"/>
       <c r="D29" s="68"/>
-      <c r="E29" s="35"/>
+      <c r="E29" s="35" t="s">
+        <v>49</v>
+      </c>
       <c r="F29" s="91"/>
       <c r="G29" s="110"/>
       <c r="H29" s="3"/>
@@ -2350,11 +2314,15 @@
       <c r="R29" s="3"/>
     </row>
     <row r="30" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="35"/>
+      <c r="A30" s="35" t="s">
+        <v>75</v>
+      </c>
       <c r="B30" s="91"/>
       <c r="C30" s="91"/>
       <c r="D30" s="68"/>
-      <c r="E30" s="35"/>
+      <c r="E30" s="35" t="s">
+        <v>50</v>
+      </c>
       <c r="F30" s="91"/>
       <c r="G30" s="110"/>
       <c r="H30" s="3"/>
@@ -2370,11 +2338,15 @@
       <c r="R30" s="3"/>
     </row>
     <row r="31" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="35"/>
+      <c r="A31" s="35" t="s">
+        <v>39</v>
+      </c>
       <c r="B31" s="91"/>
       <c r="C31" s="91"/>
       <c r="D31" s="68"/>
-      <c r="E31" s="35"/>
+      <c r="E31" s="35" t="s">
+        <v>51</v>
+      </c>
       <c r="F31" s="91"/>
       <c r="G31" s="110"/>
       <c r="H31" s="3"/>
@@ -2390,11 +2362,15 @@
       <c r="R31" s="3"/>
     </row>
     <row r="32" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="35"/>
+      <c r="A32" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="B32" s="91"/>
       <c r="C32" s="91"/>
       <c r="D32" s="68"/>
-      <c r="E32" s="35"/>
+      <c r="E32" s="35" t="s">
+        <v>52</v>
+      </c>
       <c r="F32" s="91"/>
       <c r="G32" s="110"/>
       <c r="H32" s="3"/>
@@ -2410,11 +2386,15 @@
       <c r="R32" s="3"/>
     </row>
     <row r="33" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="35"/>
+      <c r="A33" s="35" t="s">
+        <v>46</v>
+      </c>
       <c r="B33" s="91"/>
       <c r="C33" s="91"/>
       <c r="D33" s="68"/>
-      <c r="E33" s="35"/>
+      <c r="E33" s="35" t="s">
+        <v>53</v>
+      </c>
       <c r="F33" s="91"/>
       <c r="G33" s="110"/>
       <c r="H33" s="3"/>
@@ -2430,11 +2410,15 @@
       <c r="R33" s="3"/>
     </row>
     <row r="34" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="35"/>
+      <c r="A34" s="35" t="s">
+        <v>98</v>
+      </c>
       <c r="B34" s="91"/>
       <c r="C34" s="91"/>
       <c r="D34" s="68"/>
-      <c r="E34" s="35"/>
+      <c r="E34" s="35" t="s">
+        <v>54</v>
+      </c>
       <c r="F34" s="91"/>
       <c r="G34" s="110"/>
       <c r="H34" s="3"/>
@@ -2450,11 +2434,15 @@
       <c r="R34" s="3"/>
     </row>
     <row r="35" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="35"/>
+      <c r="A35" s="35" t="s">
+        <v>41</v>
+      </c>
       <c r="B35" s="91"/>
       <c r="C35" s="91"/>
       <c r="D35" s="68"/>
-      <c r="E35" s="35"/>
+      <c r="E35" s="35" t="s">
+        <v>55</v>
+      </c>
       <c r="F35" s="91"/>
       <c r="G35" s="110"/>
       <c r="H35" s="3"/>
@@ -2470,15 +2458,19 @@
       <c r="R35" s="3"/>
     </row>
     <row r="36" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="35"/>
+      <c r="A36" s="35" t="s">
+        <v>42</v>
+      </c>
       <c r="B36" s="91"/>
       <c r="C36" s="91"/>
       <c r="D36" s="68"/>
-      <c r="E36" s="35"/>
+      <c r="E36" s="35" t="s">
+        <v>56</v>
+      </c>
       <c r="F36" s="91"/>
       <c r="G36" s="110"/>
       <c r="H36" s="3"/>
-      <c r="I36" s="3"/>
+      <c r="I36" s="139"/>
       <c r="J36" s="3"/>
       <c r="K36" s="3"/>
       <c r="L36" s="3"/>
@@ -2490,11 +2482,15 @@
       <c r="R36" s="3"/>
     </row>
     <row r="37" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="35"/>
+      <c r="A37" s="35" t="s">
+        <v>76</v>
+      </c>
       <c r="B37" s="91"/>
       <c r="C37" s="91"/>
       <c r="D37" s="68"/>
-      <c r="E37" s="35"/>
+      <c r="E37" s="35" t="s">
+        <v>57</v>
+      </c>
       <c r="F37" s="91"/>
       <c r="G37" s="110"/>
       <c r="H37" s="3"/>
@@ -2510,11 +2506,15 @@
       <c r="R37" s="3"/>
     </row>
     <row r="38" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="35"/>
+      <c r="A38" s="35" t="s">
+        <v>43</v>
+      </c>
       <c r="B38" s="91"/>
       <c r="C38" s="91"/>
       <c r="D38" s="68"/>
-      <c r="E38" s="35"/>
+      <c r="E38" s="35" t="s">
+        <v>58</v>
+      </c>
       <c r="F38" s="91"/>
       <c r="G38" s="110"/>
       <c r="H38" s="3"/>
@@ -2530,11 +2530,15 @@
       <c r="R38" s="3"/>
     </row>
     <row r="39" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="35"/>
+      <c r="A39" s="35" t="s">
+        <v>44</v>
+      </c>
       <c r="B39" s="91"/>
       <c r="C39" s="91"/>
       <c r="D39" s="68"/>
-      <c r="E39" s="35"/>
+      <c r="E39" s="35" t="s">
+        <v>59</v>
+      </c>
       <c r="F39" s="91"/>
       <c r="G39" s="110"/>
       <c r="H39" s="3"/>
@@ -2550,11 +2554,15 @@
       <c r="R39" s="3"/>
     </row>
     <row r="40" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="35"/>
+      <c r="A40" s="35" t="s">
+        <v>45</v>
+      </c>
       <c r="B40" s="91"/>
       <c r="C40" s="91"/>
       <c r="D40" s="68"/>
-      <c r="E40" s="35"/>
+      <c r="E40" s="35" t="s">
+        <v>60</v>
+      </c>
       <c r="F40" s="91"/>
       <c r="G40" s="110"/>
       <c r="H40" s="3"/>
@@ -2570,11 +2578,15 @@
       <c r="R40" s="3"/>
     </row>
     <row r="41" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="35"/>
+      <c r="A41" s="35" t="s">
+        <v>77</v>
+      </c>
       <c r="B41" s="91"/>
       <c r="C41" s="91"/>
       <c r="D41" s="68"/>
-      <c r="E41" s="35"/>
+      <c r="E41" s="35" t="s">
+        <v>61</v>
+      </c>
       <c r="F41" s="91"/>
       <c r="G41" s="110"/>
       <c r="H41" s="3"/>
@@ -2590,11 +2602,15 @@
       <c r="R41" s="3"/>
     </row>
     <row r="42" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="77"/>
+      <c r="A42" s="77" t="s">
+        <v>103</v>
+      </c>
       <c r="B42" s="91"/>
       <c r="C42" s="91"/>
       <c r="D42" s="68"/>
-      <c r="E42" s="32"/>
+      <c r="E42" s="32" t="s">
+        <v>104</v>
+      </c>
       <c r="F42" s="91"/>
       <c r="G42" s="110"/>
       <c r="H42" s="3"/>
@@ -2614,7 +2630,9 @@
       <c r="B43" s="91"/>
       <c r="C43" s="91"/>
       <c r="D43" s="68"/>
-      <c r="E43" s="32"/>
+      <c r="E43" s="35" t="s">
+        <v>105</v>
+      </c>
       <c r="F43" s="91"/>
       <c r="G43" s="110"/>
       <c r="H43" s="3"/>
@@ -2630,17 +2648,15 @@
       <c r="R43" s="3"/>
     </row>
     <row r="44" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="117" t="s">
-        <v>8</v>
-      </c>
-      <c r="B44" s="118"/>
-      <c r="C44" s="118"/>
-      <c r="D44" s="25"/>
-      <c r="E44" s="118" t="s">
-        <v>9</v>
-      </c>
-      <c r="F44" s="118"/>
-      <c r="G44" s="119"/>
+      <c r="A44" s="77"/>
+      <c r="B44" s="91"/>
+      <c r="C44" s="91"/>
+      <c r="D44" s="68"/>
+      <c r="E44" s="35" t="s">
+        <v>106</v>
+      </c>
+      <c r="F44" s="91"/>
+      <c r="G44" s="110"/>
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>
       <c r="J44" s="3"/>
@@ -2653,26 +2669,16 @@
       <c r="Q44" s="3"/>
       <c r="R44" s="3"/>
     </row>
-    <row r="45" spans="1:18" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="B45" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D45" s="25"/>
-      <c r="E45" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="F45" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="G45" s="20" t="s">
-        <v>2</v>
-      </c>
+    <row r="45" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="77"/>
+      <c r="B45" s="91"/>
+      <c r="C45" s="91"/>
+      <c r="D45" s="68"/>
+      <c r="E45" s="35" t="s">
+        <v>107</v>
+      </c>
+      <c r="F45" s="91"/>
+      <c r="G45" s="110"/>
       <c r="H45" s="3"/>
       <c r="I45" s="3"/>
       <c r="J45" s="3"/>
@@ -2685,14 +2691,18 @@
       <c r="Q45" s="3"/>
       <c r="R45" s="3"/>
     </row>
-    <row r="46" spans="1:18" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="35"/>
-      <c r="B46" s="97"/>
-      <c r="C46" s="98"/>
-      <c r="D46" s="78"/>
-      <c r="E46" s="74"/>
-      <c r="F46" s="106"/>
-      <c r="G46" s="107"/>
+    <row r="46" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="117" t="s">
+        <v>8</v>
+      </c>
+      <c r="B46" s="118"/>
+      <c r="C46" s="118"/>
+      <c r="D46" s="25"/>
+      <c r="E46" s="118" t="s">
+        <v>9</v>
+      </c>
+      <c r="F46" s="118"/>
+      <c r="G46" s="119"/>
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
       <c r="J46" s="3"/>
@@ -2706,13 +2716,25 @@
       <c r="R46" s="3"/>
     </row>
     <row r="47" spans="1:18" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="35"/>
-      <c r="B47" s="97"/>
-      <c r="C47" s="98"/>
-      <c r="D47" s="78"/>
-      <c r="E47" s="74"/>
-      <c r="F47" s="106"/>
-      <c r="G47" s="107"/>
+      <c r="A47" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D47" s="25"/>
+      <c r="E47" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F47" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="G47" s="20" t="s">
+        <v>2</v>
+      </c>
       <c r="H47" s="3"/>
       <c r="I47" s="3"/>
       <c r="J47" s="3"/>
@@ -2726,11 +2748,15 @@
       <c r="R47" s="3"/>
     </row>
     <row r="48" spans="1:18" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="74"/>
+      <c r="A48" s="35" t="s">
+        <v>62</v>
+      </c>
       <c r="B48" s="97"/>
       <c r="C48" s="98"/>
-      <c r="D48" s="73"/>
-      <c r="E48" s="79"/>
+      <c r="D48" s="78"/>
+      <c r="E48" s="74" t="s">
+        <v>65</v>
+      </c>
       <c r="F48" s="106"/>
       <c r="G48" s="107"/>
       <c r="H48" s="3"/>
@@ -2746,11 +2772,15 @@
       <c r="R48" s="3"/>
     </row>
     <row r="49" spans="1:18" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="80"/>
+      <c r="A49" s="35" t="s">
+        <v>78</v>
+      </c>
       <c r="B49" s="97"/>
       <c r="C49" s="98"/>
-      <c r="D49" s="73"/>
-      <c r="E49" s="79"/>
+      <c r="D49" s="78"/>
+      <c r="E49" s="74" t="s">
+        <v>66</v>
+      </c>
       <c r="F49" s="106"/>
       <c r="G49" s="107"/>
       <c r="H49" s="3"/>
@@ -2766,7 +2796,9 @@
       <c r="R49" s="3"/>
     </row>
     <row r="50" spans="1:18" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="80"/>
+      <c r="A50" s="35" t="s">
+        <v>108</v>
+      </c>
       <c r="B50" s="97"/>
       <c r="C50" s="98"/>
       <c r="D50" s="73"/>
@@ -2786,11 +2818,13 @@
       <c r="R50" s="3"/>
     </row>
     <row r="51" spans="1:18" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="80"/>
+      <c r="A51" s="35" t="s">
+        <v>109</v>
+      </c>
       <c r="B51" s="97"/>
       <c r="C51" s="98"/>
-      <c r="D51" s="78"/>
-      <c r="E51" s="74"/>
+      <c r="D51" s="73"/>
+      <c r="E51" s="79"/>
       <c r="F51" s="106"/>
       <c r="G51" s="107"/>
       <c r="H51" s="3"/>
@@ -2805,84 +2839,110 @@
       <c r="Q51" s="3"/>
       <c r="R51" s="3"/>
     </row>
-    <row r="52" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="117" t="s">
+    <row r="52" spans="1:18" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="80"/>
+      <c r="B52" s="97"/>
+      <c r="C52" s="98"/>
+      <c r="D52" s="73"/>
+      <c r="E52" s="79"/>
+      <c r="F52" s="106"/>
+      <c r="G52" s="107"/>
+      <c r="H52" s="3"/>
+      <c r="I52" s="3"/>
+      <c r="J52" s="3"/>
+      <c r="K52" s="3"/>
+      <c r="L52" s="3"/>
+      <c r="M52" s="3"/>
+      <c r="N52" s="3"/>
+      <c r="O52" s="3"/>
+      <c r="P52" s="3"/>
+      <c r="Q52" s="3"/>
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="1:18" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="80"/>
+      <c r="B53" s="97"/>
+      <c r="C53" s="98"/>
+      <c r="D53" s="78"/>
+      <c r="E53" s="74"/>
+      <c r="F53" s="106"/>
+      <c r="G53" s="107"/>
+      <c r="H53" s="3"/>
+      <c r="I53" s="3"/>
+      <c r="J53" s="3"/>
+      <c r="K53" s="3"/>
+      <c r="L53" s="3"/>
+      <c r="M53" s="3"/>
+      <c r="N53" s="3"/>
+      <c r="O53" s="3"/>
+      <c r="P53" s="3"/>
+      <c r="Q53" s="3"/>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="117" t="s">
         <v>11</v>
       </c>
-      <c r="B52" s="118"/>
-      <c r="C52" s="118"/>
-      <c r="D52" s="24"/>
-      <c r="E52" s="123" t="s">
+      <c r="B54" s="118"/>
+      <c r="C54" s="118"/>
+      <c r="D54" s="24"/>
+      <c r="E54" s="123" t="s">
         <v>10</v>
       </c>
-      <c r="F52" s="124"/>
-      <c r="G52" s="125"/>
-    </row>
-    <row r="53" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="19" t="s">
+      <c r="F54" s="124"/>
+      <c r="G54" s="125"/>
+    </row>
+    <row r="55" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="B53" s="10" t="s">
+      <c r="B55" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C53" s="4" t="s">
+      <c r="C55" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D53" s="24"/>
-      <c r="E53" s="13" t="s">
+      <c r="D55" s="24"/>
+      <c r="E55" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F53" s="7" t="s">
+      <c r="F55" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="G53" s="20" t="s">
+      <c r="G55" s="20" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="35"/>
-      <c r="B54" s="97"/>
-      <c r="C54" s="98"/>
-      <c r="D54" s="73"/>
-      <c r="E54" s="79"/>
-      <c r="F54" s="106"/>
-      <c r="G54" s="107"/>
-    </row>
-    <row r="55" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="35"/>
-      <c r="B55" s="97"/>
-      <c r="C55" s="98"/>
-      <c r="D55" s="73"/>
-      <c r="E55" s="79"/>
-      <c r="F55" s="106"/>
-      <c r="G55" s="107"/>
-    </row>
     <row r="56" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="80"/>
+      <c r="A56" s="35" t="s">
+        <v>63</v>
+      </c>
       <c r="B56" s="97"/>
       <c r="C56" s="98"/>
-      <c r="D56" s="81"/>
+      <c r="D56" s="73"/>
       <c r="E56" s="79"/>
       <c r="F56" s="106"/>
       <c r="G56" s="107"/>
     </row>
     <row r="57" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="82"/>
-      <c r="B57" s="101"/>
-      <c r="C57" s="102"/>
-      <c r="D57" s="81"/>
-      <c r="E57" s="83"/>
-      <c r="F57" s="91"/>
-      <c r="G57" s="110"/>
+      <c r="A57" s="35" t="s">
+        <v>64</v>
+      </c>
+      <c r="B57" s="97"/>
+      <c r="C57" s="98"/>
+      <c r="D57" s="73"/>
+      <c r="E57" s="79"/>
+      <c r="F57" s="106"/>
+      <c r="G57" s="107"/>
     </row>
     <row r="58" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="82"/>
-      <c r="B58" s="101"/>
-      <c r="C58" s="102"/>
+      <c r="A58" s="80"/>
+      <c r="B58" s="97"/>
+      <c r="C58" s="98"/>
       <c r="D58" s="81"/>
-      <c r="E58" s="83"/>
-      <c r="F58" s="91"/>
-      <c r="G58" s="110"/>
+      <c r="E58" s="79"/>
+      <c r="F58" s="106"/>
+      <c r="G58" s="107"/>
     </row>
     <row r="59" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="82"/>
@@ -2942,8 +3002,8 @@
       <c r="A65" s="82"/>
       <c r="B65" s="101"/>
       <c r="C65" s="102"/>
-      <c r="D65" s="85"/>
-      <c r="E65" s="84"/>
+      <c r="D65" s="81"/>
+      <c r="E65" s="83"/>
       <c r="F65" s="91"/>
       <c r="G65" s="110"/>
     </row>
@@ -2951,8 +3011,8 @@
       <c r="A66" s="82"/>
       <c r="B66" s="101"/>
       <c r="C66" s="102"/>
-      <c r="D66" s="85"/>
-      <c r="E66" s="84"/>
+      <c r="D66" s="81"/>
+      <c r="E66" s="83"/>
       <c r="F66" s="91"/>
       <c r="G66" s="110"/>
     </row>
@@ -2969,22 +3029,38 @@
       <c r="A68" s="82"/>
       <c r="B68" s="101"/>
       <c r="C68" s="102"/>
-      <c r="D68" s="86"/>
+      <c r="D68" s="85"/>
       <c r="E68" s="84"/>
       <c r="F68" s="91"/>
       <c r="G68" s="110"/>
     </row>
-    <row r="69" spans="1:7" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="87"/>
-      <c r="B69" s="88"/>
-      <c r="C69" s="88"/>
-      <c r="D69" s="89"/>
-      <c r="E69" s="90"/>
-      <c r="F69" s="111"/>
-      <c r="G69" s="112"/>
-    </row>
-    <row r="70" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="71" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="69" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="82"/>
+      <c r="B69" s="101"/>
+      <c r="C69" s="102"/>
+      <c r="D69" s="85"/>
+      <c r="E69" s="84"/>
+      <c r="F69" s="91"/>
+      <c r="G69" s="110"/>
+    </row>
+    <row r="70" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="82"/>
+      <c r="B70" s="101"/>
+      <c r="C70" s="102"/>
+      <c r="D70" s="86"/>
+      <c r="E70" s="84"/>
+      <c r="F70" s="91"/>
+      <c r="G70" s="110"/>
+    </row>
+    <row r="71" spans="1:7" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="87"/>
+      <c r="B71" s="88"/>
+      <c r="C71" s="88"/>
+      <c r="D71" s="89"/>
+      <c r="E71" s="90"/>
+      <c r="F71" s="111"/>
+      <c r="G71" s="112"/>
+    </row>
     <row r="72" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="73" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="74" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -3903,2304 +3979,16 @@
     <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-  </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="A52:C52"/>
-    <mergeCell ref="E52:G52"/>
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="E15:G15"/>
-    <mergeCell ref="A24:G24"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="E44:G44"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.25" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:R989"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="30.5" style="2" customWidth="1"/>
-    <col min="2" max="2" width="21" style="103" customWidth="1"/>
-    <col min="3" max="3" width="20" style="103" customWidth="1"/>
-    <col min="4" max="4" width="6.5" style="2" customWidth="1"/>
-    <col min="5" max="5" width="40.33203125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="28.6640625" style="103" customWidth="1"/>
-    <col min="7" max="7" width="19.83203125" style="103" customWidth="1"/>
-    <col min="8" max="8" width="19.5" style="2" customWidth="1"/>
-    <col min="9" max="9" width="26.1640625" style="2" customWidth="1"/>
-    <col min="10" max="18" width="8.83203125" style="2" customWidth="1"/>
-    <col min="19" max="16384" width="14.5" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:15" ht="60.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="31"/>
-      <c r="B1" s="113" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="114"/>
-      <c r="D1" s="115"/>
-      <c r="E1" s="115"/>
-      <c r="F1" s="115"/>
-      <c r="G1" s="116"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-    </row>
-    <row r="2" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="126" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="126"/>
-      <c r="C2" s="126"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="56"/>
-      <c r="G2" s="104"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
-      <c r="O2" s="3"/>
-    </row>
-    <row r="3" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="27"/>
-      <c r="E3" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="G3" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3"/>
-      <c r="O3" s="3"/>
-    </row>
-    <row r="4" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="35" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="91"/>
-      <c r="C4" s="91"/>
-      <c r="D4" s="68"/>
-      <c r="E4" s="35" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" s="92"/>
-      <c r="G4" s="105"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
-      <c r="N4" s="3"/>
-      <c r="O4" s="3"/>
-    </row>
-    <row r="5" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="35" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="92"/>
-      <c r="C5" s="93"/>
-      <c r="D5" s="69"/>
-      <c r="E5" s="35" t="s">
-        <v>69</v>
-      </c>
-      <c r="F5" s="92"/>
-      <c r="G5" s="105"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
-      <c r="N5" s="3"/>
-      <c r="O5" s="3"/>
-    </row>
-    <row r="6" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="35" t="s">
-        <v>67</v>
-      </c>
-      <c r="B6" s="92"/>
-      <c r="C6" s="93"/>
-      <c r="D6" s="69"/>
-      <c r="E6" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6" s="92"/>
-      <c r="G6" s="105"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
-      <c r="N6" s="3"/>
-      <c r="O6" s="3"/>
-    </row>
-    <row r="7" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="35" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="92"/>
-      <c r="C7" s="93"/>
-      <c r="D7" s="69"/>
-      <c r="E7" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="F7" s="92"/>
-      <c r="G7" s="105"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
-      <c r="N7" s="3"/>
-      <c r="O7" s="3"/>
-    </row>
-    <row r="8" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="35" t="s">
-        <v>68</v>
-      </c>
-      <c r="B8" s="92"/>
-      <c r="C8" s="93"/>
-      <c r="D8" s="69"/>
-      <c r="E8" s="35" t="s">
-        <v>20</v>
-      </c>
-      <c r="F8" s="92"/>
-      <c r="G8" s="105"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
-      <c r="N8" s="3"/>
-      <c r="O8" s="3"/>
-    </row>
-    <row r="9" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="35" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="94"/>
-      <c r="C9" s="95"/>
-      <c r="D9" s="70"/>
-      <c r="E9" s="35" t="s">
-        <v>21</v>
-      </c>
-      <c r="F9" s="92"/>
-      <c r="G9" s="105"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
-      <c r="N9" s="3"/>
-      <c r="O9" s="3"/>
-    </row>
-    <row r="10" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="35" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10" s="92"/>
-      <c r="C10" s="93"/>
-      <c r="D10" s="69"/>
-      <c r="E10" s="35" t="s">
-        <v>22</v>
-      </c>
-      <c r="F10" s="92"/>
-      <c r="G10" s="105"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
-      <c r="M10" s="3"/>
-      <c r="N10" s="3"/>
-      <c r="O10" s="3"/>
-    </row>
-    <row r="11" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" s="92"/>
-      <c r="C11" s="93"/>
-      <c r="D11" s="69"/>
-      <c r="E11" s="35" t="s">
-        <v>23</v>
-      </c>
-      <c r="F11" s="92"/>
-      <c r="G11" s="105"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
-      <c r="N11" s="3"/>
-      <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="35" t="s">
-        <v>26</v>
-      </c>
-      <c r="B12" s="92"/>
-      <c r="C12" s="93"/>
-      <c r="D12" s="69"/>
-      <c r="E12" s="35" t="s">
-        <v>70</v>
-      </c>
-      <c r="F12" s="92"/>
-      <c r="G12" s="105"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
-      <c r="N12" s="3"/>
-      <c r="O12" s="3"/>
-    </row>
-    <row r="13" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="34"/>
-      <c r="B13" s="92"/>
-      <c r="C13" s="93"/>
-      <c r="D13" s="69"/>
-      <c r="E13" s="35" t="s">
-        <v>71</v>
-      </c>
-      <c r="F13" s="92"/>
-      <c r="G13" s="105"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
-      <c r="N13" s="3"/>
-      <c r="O13" s="3"/>
-    </row>
-    <row r="14" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="33"/>
-      <c r="B14" s="96"/>
-      <c r="C14" s="93"/>
-      <c r="D14" s="71"/>
-      <c r="E14" s="72"/>
-      <c r="F14" s="92"/>
-      <c r="G14" s="105"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
-      <c r="M14" s="3"/>
-      <c r="N14" s="3"/>
-      <c r="O14" s="3"/>
-    </row>
-    <row r="15" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="127" t="s">
-        <v>6</v>
-      </c>
-      <c r="B15" s="128"/>
-      <c r="C15" s="129"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="123" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" s="124"/>
-      <c r="G15" s="125"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
-      <c r="M15" s="3"/>
-      <c r="N15" s="3"/>
-      <c r="O15" s="3"/>
-    </row>
-    <row r="16" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="B16" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="D16" s="30"/>
-      <c r="E16" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="G16" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
-      <c r="M16" s="3"/>
-      <c r="N16" s="3"/>
-      <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="35" t="s">
-        <v>27</v>
-      </c>
-      <c r="B17" s="97"/>
-      <c r="C17" s="98"/>
-      <c r="D17" s="73"/>
-      <c r="E17" s="35" t="s">
-        <v>32</v>
-      </c>
-      <c r="F17" s="106"/>
-      <c r="G17" s="107"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="3"/>
-      <c r="L17" s="3"/>
-      <c r="M17" s="3"/>
-      <c r="N17" s="3"/>
-      <c r="O17" s="3"/>
-    </row>
-    <row r="18" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="35" t="s">
-        <v>28</v>
-      </c>
-      <c r="B18" s="97"/>
-      <c r="C18" s="98"/>
-      <c r="D18" s="73"/>
-      <c r="E18" s="35" t="s">
-        <v>33</v>
-      </c>
-      <c r="F18" s="106"/>
-      <c r="G18" s="107"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
-      <c r="L18" s="3"/>
-      <c r="M18" s="3"/>
-      <c r="N18" s="3"/>
-      <c r="O18" s="3"/>
-    </row>
-    <row r="19" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="35" t="s">
-        <v>29</v>
-      </c>
-      <c r="B19" s="97"/>
-      <c r="C19" s="98"/>
-      <c r="D19" s="73"/>
-      <c r="E19" s="35" t="s">
-        <v>34</v>
-      </c>
-      <c r="F19" s="106"/>
-      <c r="G19" s="107"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
-      <c r="K19" s="3"/>
-      <c r="L19" s="3"/>
-      <c r="M19" s="3"/>
-      <c r="N19" s="3"/>
-      <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="35" t="s">
-        <v>30</v>
-      </c>
-      <c r="B20" s="97"/>
-      <c r="C20" s="98"/>
-      <c r="D20" s="73"/>
-      <c r="E20" s="35" t="s">
-        <v>35</v>
-      </c>
-      <c r="F20" s="106"/>
-      <c r="G20" s="107"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
-      <c r="J20" s="3"/>
-      <c r="K20" s="3"/>
-      <c r="L20" s="3"/>
-      <c r="M20" s="3"/>
-      <c r="N20" s="3"/>
-      <c r="O20" s="3"/>
-    </row>
-    <row r="21" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="B21" s="96"/>
-      <c r="C21" s="93"/>
-      <c r="D21" s="71"/>
-      <c r="E21" s="35" t="s">
-        <v>36</v>
-      </c>
-      <c r="F21" s="92"/>
-      <c r="G21" s="105"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
-      <c r="J21" s="3"/>
-      <c r="K21" s="3"/>
-      <c r="L21" s="3"/>
-      <c r="M21" s="3"/>
-      <c r="N21" s="3"/>
-      <c r="O21" s="3"/>
-    </row>
-    <row r="22" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="33"/>
-      <c r="B22" s="96"/>
-      <c r="C22" s="93"/>
-      <c r="D22" s="71"/>
-      <c r="E22" s="34"/>
-      <c r="F22" s="92"/>
-      <c r="G22" s="105"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
-      <c r="J22" s="3"/>
-      <c r="K22" s="3"/>
-      <c r="L22" s="3"/>
-      <c r="M22" s="3"/>
-      <c r="N22" s="3"/>
-      <c r="O22" s="3"/>
-    </row>
-    <row r="23" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="75"/>
-      <c r="B23" s="99"/>
-      <c r="C23" s="100"/>
-      <c r="D23" s="71"/>
-      <c r="E23" s="76"/>
-      <c r="F23" s="108"/>
-      <c r="G23" s="109"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
-      <c r="J23" s="3"/>
-      <c r="K23" s="3"/>
-      <c r="L23" s="3"/>
-      <c r="M23" s="3"/>
-      <c r="N23" s="3"/>
-      <c r="O23" s="3"/>
-    </row>
-    <row r="24" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="120" t="s">
-        <v>12</v>
-      </c>
-      <c r="B24" s="121"/>
-      <c r="C24" s="121"/>
-      <c r="D24" s="121"/>
-      <c r="E24" s="121"/>
-      <c r="F24" s="121"/>
-      <c r="G24" s="122"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
-      <c r="J24" s="3"/>
-      <c r="K24" s="3"/>
-      <c r="L24" s="3"/>
-      <c r="M24" s="3"/>
-      <c r="N24" s="3"/>
-      <c r="O24" s="3"/>
-      <c r="P24" s="3"/>
-      <c r="Q24" s="3"/>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="22" t="s">
-        <v>4</v>
-      </c>
-      <c r="B25" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="C25" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="D25" s="25"/>
-      <c r="E25" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="F25" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="G25" s="23" t="s">
-        <v>2</v>
-      </c>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
-      <c r="J25" s="3"/>
-      <c r="K25" s="3"/>
-      <c r="L25" s="3"/>
-      <c r="M25" s="3"/>
-      <c r="N25" s="3"/>
-      <c r="O25" s="3"/>
-      <c r="P25" s="3"/>
-      <c r="Q25" s="3"/>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="35" t="s">
-        <v>72</v>
-      </c>
-      <c r="B26" s="91"/>
-      <c r="C26" s="91"/>
-      <c r="D26" s="68"/>
-      <c r="E26" s="35" t="s">
-        <v>47</v>
-      </c>
-      <c r="F26" s="91"/>
-      <c r="G26" s="110"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
-      <c r="J26" s="3"/>
-      <c r="K26" s="3"/>
-      <c r="L26" s="3"/>
-      <c r="M26" s="3"/>
-      <c r="N26" s="3"/>
-      <c r="O26" s="3"/>
-      <c r="P26" s="3"/>
-      <c r="Q26" s="3"/>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="35" t="s">
-        <v>37</v>
-      </c>
-      <c r="B27" s="91"/>
-      <c r="C27" s="91"/>
-      <c r="D27" s="68"/>
-      <c r="E27" s="35" t="s">
-        <v>48</v>
-      </c>
-      <c r="F27" s="91"/>
-      <c r="G27" s="110"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
-      <c r="J27" s="3"/>
-      <c r="K27" s="3"/>
-      <c r="L27" s="3"/>
-      <c r="M27" s="3"/>
-      <c r="N27" s="3"/>
-      <c r="O27" s="3"/>
-      <c r="P27" s="3"/>
-      <c r="Q27" s="3"/>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="35" t="s">
-        <v>38</v>
-      </c>
-      <c r="B28" s="91"/>
-      <c r="C28" s="91"/>
-      <c r="D28" s="68"/>
-      <c r="E28" s="35" t="s">
-        <v>73</v>
-      </c>
-      <c r="F28" s="91"/>
-      <c r="G28" s="110"/>
-      <c r="H28" s="3"/>
-      <c r="I28" s="3"/>
-      <c r="J28" s="3"/>
-      <c r="K28" s="3"/>
-      <c r="L28" s="3"/>
-      <c r="M28" s="3"/>
-      <c r="N28" s="3"/>
-      <c r="O28" s="3"/>
-      <c r="P28" s="3"/>
-      <c r="Q28" s="3"/>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="35" t="s">
-        <v>74</v>
-      </c>
-      <c r="B29" s="91"/>
-      <c r="C29" s="91"/>
-      <c r="D29" s="68"/>
-      <c r="E29" s="35" t="s">
-        <v>49</v>
-      </c>
-      <c r="F29" s="91"/>
-      <c r="G29" s="110"/>
-      <c r="H29" s="3"/>
-      <c r="I29" s="3"/>
-      <c r="J29" s="3"/>
-      <c r="K29" s="3"/>
-      <c r="L29" s="3"/>
-      <c r="M29" s="3"/>
-      <c r="N29" s="3"/>
-      <c r="O29" s="3"/>
-      <c r="P29" s="3"/>
-      <c r="Q29" s="3"/>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="35" t="s">
-        <v>75</v>
-      </c>
-      <c r="B30" s="91"/>
-      <c r="C30" s="91"/>
-      <c r="D30" s="68"/>
-      <c r="E30" s="35" t="s">
-        <v>50</v>
-      </c>
-      <c r="F30" s="91"/>
-      <c r="G30" s="110"/>
-      <c r="H30" s="3"/>
-      <c r="I30" s="3"/>
-      <c r="J30" s="3"/>
-      <c r="K30" s="3"/>
-      <c r="L30" s="3"/>
-      <c r="M30" s="3"/>
-      <c r="N30" s="3"/>
-      <c r="O30" s="3"/>
-      <c r="P30" s="3"/>
-      <c r="Q30" s="3"/>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="35" t="s">
-        <v>39</v>
-      </c>
-      <c r="B31" s="91"/>
-      <c r="C31" s="91"/>
-      <c r="D31" s="68"/>
-      <c r="E31" s="35" t="s">
-        <v>51</v>
-      </c>
-      <c r="F31" s="91"/>
-      <c r="G31" s="110"/>
-      <c r="H31" s="3"/>
-      <c r="I31" s="3"/>
-      <c r="J31" s="3"/>
-      <c r="K31" s="3"/>
-      <c r="L31" s="3"/>
-      <c r="M31" s="3"/>
-      <c r="N31" s="3"/>
-      <c r="O31" s="3"/>
-      <c r="P31" s="3"/>
-      <c r="Q31" s="3"/>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="35" t="s">
-        <v>40</v>
-      </c>
-      <c r="B32" s="91"/>
-      <c r="C32" s="91"/>
-      <c r="D32" s="68"/>
-      <c r="E32" s="35" t="s">
-        <v>52</v>
-      </c>
-      <c r="F32" s="91"/>
-      <c r="G32" s="110"/>
-      <c r="H32" s="3"/>
-      <c r="I32" s="3"/>
-      <c r="J32" s="3"/>
-      <c r="K32" s="3"/>
-      <c r="L32" s="3"/>
-      <c r="M32" s="3"/>
-      <c r="N32" s="3"/>
-      <c r="O32" s="3"/>
-      <c r="P32" s="3"/>
-      <c r="Q32" s="3"/>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="35" t="s">
-        <v>46</v>
-      </c>
-      <c r="B33" s="91"/>
-      <c r="C33" s="91"/>
-      <c r="D33" s="68"/>
-      <c r="E33" s="35" t="s">
-        <v>53</v>
-      </c>
-      <c r="F33" s="91"/>
-      <c r="G33" s="110"/>
-      <c r="H33" s="3"/>
-      <c r="I33" s="3"/>
-      <c r="J33" s="3"/>
-      <c r="K33" s="3"/>
-      <c r="L33" s="3"/>
-      <c r="M33" s="3"/>
-      <c r="N33" s="3"/>
-      <c r="O33" s="3"/>
-      <c r="P33" s="3"/>
-      <c r="Q33" s="3"/>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="35" t="s">
-        <v>98</v>
-      </c>
-      <c r="B34" s="91"/>
-      <c r="C34" s="91"/>
-      <c r="D34" s="68"/>
-      <c r="E34" s="35" t="s">
-        <v>54</v>
-      </c>
-      <c r="F34" s="91"/>
-      <c r="G34" s="110"/>
-      <c r="H34" s="3"/>
-      <c r="I34" s="3"/>
-      <c r="J34" s="3"/>
-      <c r="K34" s="3"/>
-      <c r="L34" s="3"/>
-      <c r="M34" s="3"/>
-      <c r="N34" s="3"/>
-      <c r="O34" s="3"/>
-      <c r="P34" s="3"/>
-      <c r="Q34" s="3"/>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="35" t="s">
-        <v>41</v>
-      </c>
-      <c r="B35" s="91"/>
-      <c r="C35" s="91"/>
-      <c r="D35" s="68"/>
-      <c r="E35" s="35" t="s">
-        <v>55</v>
-      </c>
-      <c r="F35" s="91"/>
-      <c r="G35" s="110"/>
-      <c r="H35" s="3"/>
-      <c r="I35" s="3"/>
-      <c r="J35" s="3"/>
-      <c r="K35" s="3"/>
-      <c r="L35" s="3"/>
-      <c r="M35" s="3"/>
-      <c r="N35" s="3"/>
-      <c r="O35" s="3"/>
-      <c r="P35" s="3"/>
-      <c r="Q35" s="3"/>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="36" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="35" t="s">
-        <v>42</v>
-      </c>
-      <c r="B36" s="91"/>
-      <c r="C36" s="91"/>
-      <c r="D36" s="68"/>
-      <c r="E36" s="35" t="s">
-        <v>56</v>
-      </c>
-      <c r="F36" s="91"/>
-      <c r="G36" s="110"/>
-      <c r="H36" s="3"/>
-      <c r="I36" s="3"/>
-      <c r="J36" s="3"/>
-      <c r="K36" s="3"/>
-      <c r="L36" s="3"/>
-      <c r="M36" s="3"/>
-      <c r="N36" s="3"/>
-      <c r="O36" s="3"/>
-      <c r="P36" s="3"/>
-      <c r="Q36" s="3"/>
-      <c r="R36" s="3"/>
-    </row>
-    <row r="37" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="35" t="s">
-        <v>76</v>
-      </c>
-      <c r="B37" s="91"/>
-      <c r="C37" s="91"/>
-      <c r="D37" s="68"/>
-      <c r="E37" s="35" t="s">
-        <v>57</v>
-      </c>
-      <c r="F37" s="91"/>
-      <c r="G37" s="110"/>
-      <c r="H37" s="3"/>
-      <c r="I37" s="3"/>
-      <c r="J37" s="3"/>
-      <c r="K37" s="3"/>
-      <c r="L37" s="3"/>
-      <c r="M37" s="3"/>
-      <c r="N37" s="3"/>
-      <c r="O37" s="3"/>
-      <c r="P37" s="3"/>
-      <c r="Q37" s="3"/>
-      <c r="R37" s="3"/>
-    </row>
-    <row r="38" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="35" t="s">
-        <v>43</v>
-      </c>
-      <c r="B38" s="91"/>
-      <c r="C38" s="91"/>
-      <c r="D38" s="68"/>
-      <c r="E38" s="35" t="s">
-        <v>58</v>
-      </c>
-      <c r="F38" s="91"/>
-      <c r="G38" s="110"/>
-      <c r="H38" s="3"/>
-      <c r="I38" s="3"/>
-      <c r="J38" s="3"/>
-      <c r="K38" s="3"/>
-      <c r="L38" s="3"/>
-      <c r="M38" s="3"/>
-      <c r="N38" s="3"/>
-      <c r="O38" s="3"/>
-      <c r="P38" s="3"/>
-      <c r="Q38" s="3"/>
-      <c r="R38" s="3"/>
-    </row>
-    <row r="39" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="35" t="s">
-        <v>44</v>
-      </c>
-      <c r="B39" s="91"/>
-      <c r="C39" s="91"/>
-      <c r="D39" s="68"/>
-      <c r="E39" s="35" t="s">
-        <v>59</v>
-      </c>
-      <c r="F39" s="91"/>
-      <c r="G39" s="110"/>
-      <c r="H39" s="3"/>
-      <c r="I39" s="3"/>
-      <c r="J39" s="3"/>
-      <c r="K39" s="3"/>
-      <c r="L39" s="3"/>
-      <c r="M39" s="3"/>
-      <c r="N39" s="3"/>
-      <c r="O39" s="3"/>
-      <c r="P39" s="3"/>
-      <c r="Q39" s="3"/>
-      <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="35" t="s">
-        <v>45</v>
-      </c>
-      <c r="B40" s="91"/>
-      <c r="C40" s="91"/>
-      <c r="D40" s="68"/>
-      <c r="E40" s="35" t="s">
-        <v>60</v>
-      </c>
-      <c r="F40" s="91"/>
-      <c r="G40" s="110"/>
-      <c r="H40" s="3"/>
-      <c r="I40" s="3"/>
-      <c r="J40" s="3"/>
-      <c r="K40" s="3"/>
-      <c r="L40" s="3"/>
-      <c r="M40" s="3"/>
-      <c r="N40" s="3"/>
-      <c r="O40" s="3"/>
-      <c r="P40" s="3"/>
-      <c r="Q40" s="3"/>
-      <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="35" t="s">
-        <v>77</v>
-      </c>
-      <c r="B41" s="91"/>
-      <c r="C41" s="91"/>
-      <c r="D41" s="68"/>
-      <c r="E41" s="35" t="s">
-        <v>61</v>
-      </c>
-      <c r="F41" s="91"/>
-      <c r="G41" s="110"/>
-      <c r="H41" s="3"/>
-      <c r="I41" s="3"/>
-      <c r="J41" s="3"/>
-      <c r="K41" s="3"/>
-      <c r="L41" s="3"/>
-      <c r="M41" s="3"/>
-      <c r="N41" s="3"/>
-      <c r="O41" s="3"/>
-      <c r="P41" s="3"/>
-      <c r="Q41" s="3"/>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="77" t="s">
-        <v>103</v>
-      </c>
-      <c r="B42" s="91"/>
-      <c r="C42" s="91"/>
-      <c r="D42" s="68"/>
-      <c r="E42" s="32" t="s">
-        <v>104</v>
-      </c>
-      <c r="F42" s="91"/>
-      <c r="G42" s="110"/>
-      <c r="H42" s="3"/>
-      <c r="I42" s="3"/>
-      <c r="J42" s="3"/>
-      <c r="K42" s="3"/>
-      <c r="L42" s="3"/>
-      <c r="M42" s="3"/>
-      <c r="N42" s="3"/>
-      <c r="O42" s="3"/>
-      <c r="P42" s="3"/>
-      <c r="Q42" s="3"/>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="77"/>
-      <c r="B43" s="91"/>
-      <c r="C43" s="91"/>
-      <c r="D43" s="68"/>
-      <c r="E43" s="32"/>
-      <c r="F43" s="91"/>
-      <c r="G43" s="110"/>
-      <c r="H43" s="3"/>
-      <c r="I43" s="3"/>
-      <c r="J43" s="3"/>
-      <c r="K43" s="3"/>
-      <c r="L43" s="3"/>
-      <c r="M43" s="3"/>
-      <c r="N43" s="3"/>
-      <c r="O43" s="3"/>
-      <c r="P43" s="3"/>
-      <c r="Q43" s="3"/>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="117" t="s">
-        <v>8</v>
-      </c>
-      <c r="B44" s="118"/>
-      <c r="C44" s="118"/>
-      <c r="D44" s="25"/>
-      <c r="E44" s="118" t="s">
-        <v>9</v>
-      </c>
-      <c r="F44" s="118"/>
-      <c r="G44" s="119"/>
-      <c r="H44" s="3"/>
-      <c r="I44" s="3"/>
-      <c r="J44" s="3"/>
-      <c r="K44" s="3"/>
-      <c r="L44" s="3"/>
-      <c r="M44" s="3"/>
-      <c r="N44" s="3"/>
-      <c r="O44" s="3"/>
-      <c r="P44" s="3"/>
-      <c r="Q44" s="3"/>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="1:18" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="B45" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D45" s="25"/>
-      <c r="E45" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="F45" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="G45" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="H45" s="3"/>
-      <c r="I45" s="3"/>
-      <c r="J45" s="3"/>
-      <c r="K45" s="3"/>
-      <c r="L45" s="3"/>
-      <c r="M45" s="3"/>
-      <c r="N45" s="3"/>
-      <c r="O45" s="3"/>
-      <c r="P45" s="3"/>
-      <c r="Q45" s="3"/>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="1:18" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="35" t="s">
-        <v>62</v>
-      </c>
-      <c r="B46" s="97"/>
-      <c r="C46" s="98"/>
-      <c r="D46" s="78"/>
-      <c r="E46" s="74" t="s">
-        <v>65</v>
-      </c>
-      <c r="F46" s="106"/>
-      <c r="G46" s="107"/>
-      <c r="H46" s="3"/>
-      <c r="I46" s="3"/>
-      <c r="J46" s="3"/>
-      <c r="K46" s="3"/>
-      <c r="L46" s="3"/>
-      <c r="M46" s="3"/>
-      <c r="N46" s="3"/>
-      <c r="O46" s="3"/>
-      <c r="P46" s="3"/>
-      <c r="Q46" s="3"/>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="1:18" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="35" t="s">
-        <v>78</v>
-      </c>
-      <c r="B47" s="97"/>
-      <c r="C47" s="98"/>
-      <c r="D47" s="78"/>
-      <c r="E47" s="74" t="s">
-        <v>66</v>
-      </c>
-      <c r="F47" s="106"/>
-      <c r="G47" s="107"/>
-      <c r="H47" s="3"/>
-      <c r="I47" s="3"/>
-      <c r="J47" s="3"/>
-      <c r="K47" s="3"/>
-      <c r="L47" s="3"/>
-      <c r="M47" s="3"/>
-      <c r="N47" s="3"/>
-      <c r="O47" s="3"/>
-      <c r="P47" s="3"/>
-      <c r="Q47" s="3"/>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="1:18" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="74"/>
-      <c r="B48" s="97"/>
-      <c r="C48" s="98"/>
-      <c r="D48" s="73"/>
-      <c r="E48" s="79"/>
-      <c r="F48" s="106"/>
-      <c r="G48" s="107"/>
-      <c r="H48" s="3"/>
-      <c r="I48" s="3"/>
-      <c r="J48" s="3"/>
-      <c r="K48" s="3"/>
-      <c r="L48" s="3"/>
-      <c r="M48" s="3"/>
-      <c r="N48" s="3"/>
-      <c r="O48" s="3"/>
-      <c r="P48" s="3"/>
-      <c r="Q48" s="3"/>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="1:18" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="80"/>
-      <c r="B49" s="97"/>
-      <c r="C49" s="98"/>
-      <c r="D49" s="73"/>
-      <c r="E49" s="79"/>
-      <c r="F49" s="106"/>
-      <c r="G49" s="107"/>
-      <c r="H49" s="3"/>
-      <c r="I49" s="3"/>
-      <c r="J49" s="3"/>
-      <c r="K49" s="3"/>
-      <c r="L49" s="3"/>
-      <c r="M49" s="3"/>
-      <c r="N49" s="3"/>
-      <c r="O49" s="3"/>
-      <c r="P49" s="3"/>
-      <c r="Q49" s="3"/>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="1:18" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="80"/>
-      <c r="B50" s="97"/>
-      <c r="C50" s="98"/>
-      <c r="D50" s="73"/>
-      <c r="E50" s="79"/>
-      <c r="F50" s="106"/>
-      <c r="G50" s="107"/>
-      <c r="H50" s="3"/>
-      <c r="I50" s="3"/>
-      <c r="J50" s="3"/>
-      <c r="K50" s="3"/>
-      <c r="L50" s="3"/>
-      <c r="M50" s="3"/>
-      <c r="N50" s="3"/>
-      <c r="O50" s="3"/>
-      <c r="P50" s="3"/>
-      <c r="Q50" s="3"/>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="1:18" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="80"/>
-      <c r="B51" s="97"/>
-      <c r="C51" s="98"/>
-      <c r="D51" s="78"/>
-      <c r="E51" s="74"/>
-      <c r="F51" s="106"/>
-      <c r="G51" s="107"/>
-      <c r="H51" s="3"/>
-      <c r="I51" s="3"/>
-      <c r="J51" s="3"/>
-      <c r="K51" s="3"/>
-      <c r="L51" s="3"/>
-      <c r="M51" s="3"/>
-      <c r="N51" s="3"/>
-      <c r="O51" s="3"/>
-      <c r="P51" s="3"/>
-      <c r="Q51" s="3"/>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="117" t="s">
-        <v>11</v>
-      </c>
-      <c r="B52" s="118"/>
-      <c r="C52" s="118"/>
-      <c r="D52" s="24"/>
-      <c r="E52" s="123" t="s">
-        <v>10</v>
-      </c>
-      <c r="F52" s="124"/>
-      <c r="G52" s="125"/>
-    </row>
-    <row r="53" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="B53" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="C53" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D53" s="24"/>
-      <c r="E53" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F53" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="G53" s="20" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="54" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="35" t="s">
-        <v>63</v>
-      </c>
-      <c r="B54" s="97"/>
-      <c r="C54" s="98"/>
-      <c r="D54" s="73"/>
-      <c r="E54" s="79"/>
-      <c r="F54" s="106"/>
-      <c r="G54" s="107"/>
-    </row>
-    <row r="55" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="35" t="s">
-        <v>64</v>
-      </c>
-      <c r="B55" s="97"/>
-      <c r="C55" s="98"/>
-      <c r="D55" s="73"/>
-      <c r="E55" s="79"/>
-      <c r="F55" s="106"/>
-      <c r="G55" s="107"/>
-    </row>
-    <row r="56" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="80"/>
-      <c r="B56" s="97"/>
-      <c r="C56" s="98"/>
-      <c r="D56" s="81"/>
-      <c r="E56" s="79"/>
-      <c r="F56" s="106"/>
-      <c r="G56" s="107"/>
-    </row>
-    <row r="57" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="82"/>
-      <c r="B57" s="101"/>
-      <c r="C57" s="102"/>
-      <c r="D57" s="81"/>
-      <c r="E57" s="83"/>
-      <c r="F57" s="91"/>
-      <c r="G57" s="110"/>
-    </row>
-    <row r="58" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="82"/>
-      <c r="B58" s="101"/>
-      <c r="C58" s="102"/>
-      <c r="D58" s="81"/>
-      <c r="E58" s="83"/>
-      <c r="F58" s="91"/>
-      <c r="G58" s="110"/>
-    </row>
-    <row r="59" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="82"/>
-      <c r="B59" s="101"/>
-      <c r="C59" s="102"/>
-      <c r="D59" s="81"/>
-      <c r="E59" s="83"/>
-      <c r="F59" s="91"/>
-      <c r="G59" s="110"/>
-    </row>
-    <row r="60" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="82"/>
-      <c r="B60" s="101"/>
-      <c r="C60" s="102"/>
-      <c r="D60" s="81"/>
-      <c r="E60" s="83"/>
-      <c r="F60" s="91"/>
-      <c r="G60" s="110"/>
-    </row>
-    <row r="61" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="82"/>
-      <c r="B61" s="101"/>
-      <c r="C61" s="102"/>
-      <c r="D61" s="81"/>
-      <c r="E61" s="83"/>
-      <c r="F61" s="91"/>
-      <c r="G61" s="110"/>
-    </row>
-    <row r="62" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="82"/>
-      <c r="B62" s="101"/>
-      <c r="C62" s="102"/>
-      <c r="D62" s="81"/>
-      <c r="E62" s="83"/>
-      <c r="F62" s="91"/>
-      <c r="G62" s="110"/>
-    </row>
-    <row r="63" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="82"/>
-      <c r="B63" s="101"/>
-      <c r="C63" s="102"/>
-      <c r="D63" s="81"/>
-      <c r="E63" s="83"/>
-      <c r="F63" s="91"/>
-      <c r="G63" s="110"/>
-    </row>
-    <row r="64" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="82"/>
-      <c r="B64" s="101"/>
-      <c r="C64" s="102"/>
-      <c r="D64" s="81"/>
-      <c r="E64" s="83"/>
-      <c r="F64" s="91"/>
-      <c r="G64" s="110"/>
-    </row>
-    <row r="65" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="82"/>
-      <c r="B65" s="101"/>
-      <c r="C65" s="102"/>
-      <c r="D65" s="85"/>
-      <c r="E65" s="84"/>
-      <c r="F65" s="91"/>
-      <c r="G65" s="110"/>
-    </row>
-    <row r="66" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="82"/>
-      <c r="B66" s="101"/>
-      <c r="C66" s="102"/>
-      <c r="D66" s="85"/>
-      <c r="E66" s="84"/>
-      <c r="F66" s="91"/>
-      <c r="G66" s="110"/>
-    </row>
-    <row r="67" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="82"/>
-      <c r="B67" s="101"/>
-      <c r="C67" s="102"/>
-      <c r="D67" s="85"/>
-      <c r="E67" s="84"/>
-      <c r="F67" s="91"/>
-      <c r="G67" s="110"/>
-    </row>
-    <row r="68" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="82"/>
-      <c r="B68" s="101"/>
-      <c r="C68" s="102"/>
-      <c r="D68" s="86"/>
-      <c r="E68" s="84"/>
-      <c r="F68" s="91"/>
-      <c r="G68" s="110"/>
-    </row>
-    <row r="69" spans="1:7" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="87"/>
-      <c r="B69" s="88"/>
-      <c r="C69" s="88"/>
-      <c r="D69" s="89"/>
-      <c r="E69" s="90"/>
-      <c r="F69" s="111"/>
-      <c r="G69" s="112"/>
-    </row>
-    <row r="70" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="71" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="72" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="73" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="74" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="75" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="76" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="77" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="78" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="79" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="80" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="B1:G1"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="E44:G44"/>
-    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="E46:G46"/>
+    <mergeCell ref="A54:C54"/>
     <mergeCell ref="A24:G24"/>
-    <mergeCell ref="E52:G52"/>
+    <mergeCell ref="E54:G54"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="E15:G15"/>
@@ -6211,7 +3999,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9639885-A565-A84E-992A-A4144FE2AAD2}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
